--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -547,8 +547,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>23346.4</v>
+        <v>23414.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19.74</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1182.695035460993</v>
+        <v>1183.137948458818</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.03878208207507883</v>
+        <v>0.03939540346028036</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05065856129685917</v>
+        <v>0.05053057099545225</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>35.51283283003153</v>
+        <v>35.75816138411214</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>76.94172863688824</v>
+        <v>77.01532720311242</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>20.56607187463043</v>
+        <v>20.57495627298177</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24323.39110505937</v>
+        <v>24343.01155444553</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.041847612696577</v>
+        <v>0.03966428868023097</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>22.29250037743454</v>
+        <v>22.30001794527029</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26365.22952440414</v>
+        <v>26383.99748236191</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1293059968305237</v>
+        <v>0.1268326399833397</v>
       </c>
     </row>
     <row r="15"/>
@@ -7427,7 +7427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7518,6 +7518,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>23414.3</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0393954034603</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -547,7 +547,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>23414.3</v>
+        <v>23329</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19.79</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1183.137948458818</v>
+        <v>1183.012170385396</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.03939540346028036</v>
+        <v>0.039263777081608</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05053057099545225</v>
+        <v>0.05070993914807303</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>35.75816138411214</v>
+        <v>35.7055108326432</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>77.01532720311242</v>
+        <v>76.99953203767174</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>20.57495627298177</v>
+        <v>20.57304957086787</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24343.01155444553</v>
+        <v>24338.16802427873</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.03966428868023097</v>
+        <v>0.04325809182899931</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>22.30001794527029</v>
+        <v>22.29840458194314</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26383.99748236191</v>
+        <v>26379.2840006162</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1268326399833397</v>
+        <v>0.1307507394494494</v>
       </c>
     </row>
     <row r="15"/>
@@ -7427,7 +7427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7551,6 +7551,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>23329</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0392637770816</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +588,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +615,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>23329</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +623,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>19.72</v>
       </c>
     </row>
@@ -612,7 +633,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.05303030303030303</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +641,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>1183.012170385396</v>
       </c>
     </row>
@@ -630,7 +651,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.039263777081608</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +669,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>94.6969696969697</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +677,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>35.7055108326432</v>
       </c>
     </row>
@@ -666,7 +687,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>76.99953203767174</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +736,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>20.57304957086787</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>24338.16802427873</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.04325809182899931</v>
       </c>
     </row>
@@ -732,17 +752,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>22.29840458194314</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>26379.2840006162</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1307507394494494</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +815,19 @@
       <c r="B18" t="n">
         <v>20</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.3794110863381257</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.2804292628723728</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.2330247834427452</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1639263551809637</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,19 +840,19 @@
       <c r="B19" t="n">
         <v>24</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.1900379979058278</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1208474326591867</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1216016486559849</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1224198770703966</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -846,19 +865,19 @@
       <c r="B20" t="n">
         <v>20</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.1068255572697771</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.0939521989345575</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1126009545572526</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1144515211675757</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0.05555555555555555</v>
       </c>
     </row>
@@ -871,19 +890,19 @@
       <c r="B21" t="n">
         <v>23</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.0627410393742764</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.060027361417227</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.08987020932283746</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.1072524436331572</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0.2105263157894737</v>
       </c>
     </row>
@@ -896,23 +915,22 @@
       <c r="B22" t="n">
         <v>23</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>0.0432896067488568</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1378754251395846</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1207882016172213</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="30" t="n">
         <v>0.07509863754171059</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="30" t="n">
         <v>0.1363636363636364</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1048,16 +1066,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>14631.1</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>32.21</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1067,16 +1085,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>15582.8</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>29.22</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1086,16 +1104,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>15721.5</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>28.33</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1105,16 +1123,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>15763.05</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>27.01</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1124,16 +1142,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>17132.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>26.25</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1143,16 +1161,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>17618.15</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>26.98</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1162,16 +1180,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>17671.65</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>25.71</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1181,16 +1199,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>16983.2</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>23.43</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1200,16 +1218,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>17354.05</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>24.11</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1219,16 +1237,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>17339.85</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>23.42</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1238,16 +1256,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>16793.9</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>21.59</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1257,16 +1275,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>17464.75</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>22.92</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1276,16 +1294,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>17102.55</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>22.01</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1295,16 +1313,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>16584.55</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>20.44</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1314,16 +1332,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>15780.25</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>19.5</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1333,16 +1351,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>17158.25</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>20.73</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1352,16 +1370,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>17759.3</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>21.2</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1371,16 +1389,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>17094.35</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>20.64</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1390,16 +1408,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>18012.2</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>21.42</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1409,16 +1427,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>18758.35</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>22.54</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1428,16 +1446,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>18105.3</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>21.79</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1447,16 +1465,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>17662.15</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>20.73</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1466,16 +1484,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>17303.95</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>20.39</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1485,16 +1503,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>17359.75</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>20.44</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1504,16 +1522,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>18065</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>20.87</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1523,16 +1541,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>18534.4</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>21.59</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1542,16 +1560,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>19189.05</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>22.36</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1561,16 +1579,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>19753.8</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>23.01</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1580,16 +1598,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>19253.8</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>21.97</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1599,16 +1617,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>19638.3</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>22.21</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1618,16 +1636,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>19079.6</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>20.45</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1637,16 +1655,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>20133.15</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>21.52</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1656,16 +1674,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>21731.4</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>23.17</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1675,16 +1693,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>21725.7</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>22.46</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1694,16 +1712,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>21982.8</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>22.7</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1713,16 +1731,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>22326.9</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>22.88</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1732,16 +1750,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>22604.85</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1751,16 +1769,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>22530.7</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>21.4</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1770,16 +1788,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>24010.6</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>22.85</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1789,16 +1807,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>24951.15</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>23.4</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1808,16 +1826,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>25235.9</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>23.47</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1827,16 +1845,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>25810.85</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>24.26</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1846,16 +1864,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>24205.35</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>22.58</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1865,16 +1883,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>24131.1</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>22.21</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1884,16 +1902,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>23644.8</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>21.79</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1903,16 +1921,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>23508.4</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>21.33</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1922,16 +1940,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>22124.7</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>19.67</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1941,16 +1959,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>23519.35</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>21.37</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1960,16 +1978,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>24334.2</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>21.94</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1979,16 +1997,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>24750.7</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>22.32</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1998,16 +2016,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>25517.05</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>22.97</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2017,16 +2035,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>24768.35</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>21.93</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2036,16 +2054,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>24426.85</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>21.46</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2055,16 +2073,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>24611.1</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>21.76</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2074,16 +2092,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>25722.1</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>22.64</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2093,16 +2111,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>26202.95</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>22.81</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2112,16 +2130,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>26129.6</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>22.75</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2131,16 +2149,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>25320.65</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>22.04</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2150,16 +2168,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>25178.65</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>22.03</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2169,16 +2187,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>22331.4</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>19.62</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2188,16 +2206,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>23997.55</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>20.94</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2207,16 +2225,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>23547.75</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>20.27</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2226,16 +2244,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>23865.75</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>20.58</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2245,16 +2263,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>24383.6</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>20.78</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2264,16 +2282,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>24080.4</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>20.36</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2375,13 +2393,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>36250</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>1078</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>16.5</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2389,12 +2407,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,C2)+1)/2)/COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2402,31 +2420,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>36341</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>1187.7</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>17.9</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2434,12 +2452,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,C3)+1)/2)/COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2447,31 +2465,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>36433</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>1413.1</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>22</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2479,12 +2497,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,C4)+1)/2)/COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2492,31 +2510,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>36525</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>1480.4</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>24.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2524,12 +2542,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,C5)+1)/2)/COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2537,31 +2555,31 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="30">
         <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>36616</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>1528.4</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>24.6</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2569,15 +2587,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,C6)+1)/2)/COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2585,31 +2603,31 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16">
+      <c r="L6" s="30">
         <f>IFERROR((B46/B6)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>36707</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>1471.4</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2617,15 +2635,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,C7)+1)/2)/COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2633,31 +2651,31 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="30">
         <f>IFERROR((B47/B7)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>36799</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>1271.6</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>19.3</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2665,15 +2683,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,C8)+1)/2)/COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2681,31 +2699,31 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16">
+      <c r="L8" s="30">
         <f>IFERROR((B48/B8)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>36891</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>1263.5</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>19.2</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2713,15 +2731,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,C9)+1)/2)/COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2729,31 +2747,31 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="30">
         <f>IFERROR((B49/B9)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>36981</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>1148.2</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>17.2</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2761,15 +2779,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,C10)+1)/2)/COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2777,31 +2795,31 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="30">
         <f>IFERROR((B50/B10)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>37072</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>1107.9</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>15.8</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2809,15 +2827,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,C11)+1)/2)/COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2825,31 +2843,31 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="30">
         <f>IFERROR((B51/B11)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>37164</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>913.85</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>13.2</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2857,15 +2875,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,C12)+1)/2)/COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2873,31 +2891,31 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="30">
         <f>IFERROR((B52/B12)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>37256</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>1059</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>15.3</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2905,15 +2923,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,C13)+1)/2)/COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2921,31 +2939,31 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="30">
         <f>IFERROR((B53/B13)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>37346</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>1129.5</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>18.1</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2953,15 +2971,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,C14)+1)/2)/COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -2969,31 +2987,31 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="30">
         <f>IFERROR((B54/B14)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>37437</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>1057.8</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>15.7</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3001,15 +3019,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,C15)+1)/2)/COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3017,31 +3035,31 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="30">
         <f>IFERROR((B55/B15)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>37529</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>963.15</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>14.3</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3049,15 +3067,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,C16)+1)/2)/COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3065,31 +3083,31 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16">
+      <c r="L16" s="30">
         <f>IFERROR((B56/B16)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>37621</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>1093.5</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>14.8</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3097,15 +3115,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,C17)+1)/2)/COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3113,31 +3131,31 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="30">
         <f>IFERROR((B57/B17)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>37711</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>978.2</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>13.4</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3145,15 +3163,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,C18)+1)/2)/COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3161,31 +3179,31 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16">
+      <c r="L18" s="30">
         <f>IFERROR((B58/B18)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>37802</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>1134.1</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>12.9</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3193,15 +3211,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,C19)+1)/2)/COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3209,31 +3227,31 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="30">
         <f>IFERROR((B59/B19)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>37894</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>1417.1</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>15.6</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3241,15 +3259,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,C20)+1)/2)/COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3257,31 +3275,31 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16">
+      <c r="L20" s="30">
         <f>IFERROR((B60/B20)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>37986</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>1879.7</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>20.7</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3289,15 +3307,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,C21)+1)/2)/COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3305,31 +3323,31 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="30">
         <f>IFERROR((B61/B21)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>38077</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>1771.9</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>20.7</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3337,15 +3355,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,C22)+1)/2)/COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3353,31 +3371,31 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="30">
         <f>IFERROR((B62/B22)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>38168</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>1505.6</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>12.6</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3385,15 +3403,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,C23)+1)/2)/COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3401,31 +3419,31 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="30">
         <f>IFERROR((B63/B23)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>38260</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>1745.5</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>14.6</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3433,15 +3451,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,C24)+1)/2)/COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3449,31 +3467,31 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16">
+      <c r="L24" s="30">
         <f>IFERROR((B64/B24)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>38352</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>2080.5</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>15.3</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3481,15 +3499,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,C25)+1)/2)/COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3497,31 +3515,31 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="30">
         <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="30">
         <f>IFERROR((B65/B25)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>38442</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>2035.6</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>14.6</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3529,15 +3547,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,C26)+1)/2)/COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3545,31 +3563,31 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16">
+      <c r="K26" s="30">
         <f>IFERROR((B46/B26)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L26" s="16">
+      <c r="L26" s="30">
         <f>IFERROR((B66/B26)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>38533</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>2220.6</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>14.3</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3577,15 +3595,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,C27)+1)/2)/COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3593,31 +3611,31 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="30">
         <f>IFERROR((B47/B27)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="30">
         <f>IFERROR((B67/B27)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>38625</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>2601.4</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>16.1</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3625,15 +3643,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,C28)+1)/2)/COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3641,31 +3659,31 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16">
+      <c r="K28" s="30">
         <f>IFERROR((B48/B28)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L28" s="16">
+      <c r="L28" s="30">
         <f>IFERROR((B68/B28)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>38717</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>2836.5</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>17.2</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3673,15 +3691,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,C29)+1)/2)/COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3689,31 +3707,31 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16">
+      <c r="K29" s="30">
         <f>IFERROR((B49/B29)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="30">
         <f>IFERROR((B69/B29)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>38807</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>3402.5</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>20.3</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3721,15 +3739,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,C30)+1)/2)/COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3737,31 +3755,31 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16">
+      <c r="K30" s="30">
         <f>IFERROR((B50/B30)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L30" s="16">
+      <c r="L30" s="30">
         <f>IFERROR((B70/B30)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>38898</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>3128.2</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>18.4</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3769,15 +3787,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,C31)+1)/2)/COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3785,31 +3803,31 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16">
+      <c r="K31" s="30">
         <f>IFERROR((B51/B31)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="30">
         <f>IFERROR((B71/B31)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>38990</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>3588.4</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>20.9</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3817,15 +3835,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,C32)+1)/2)/COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3833,31 +3851,31 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16">
+      <c r="K32" s="30">
         <f>IFERROR((B52/B32)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L32" s="16">
+      <c r="L32" s="30">
         <f>IFERROR((B72/B32)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>39082</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>3966.4</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>21.3</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3865,15 +3883,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,C33)+1)/2)/COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3881,31 +3899,31 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="30">
         <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K33" s="16">
+      <c r="K33" s="30">
         <f>IFERROR((B53/B33)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="30">
         <f>IFERROR((B73/B33)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>39172</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>3821.5</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>18.4</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3913,15 +3931,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,C34)+1)/2)/COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3929,31 +3947,31 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="30">
         <f>IFERROR((B46/B34)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="30">
         <f>IFERROR((B54/B34)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="30">
         <f>IFERROR((B74/B34)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>39263</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>4318.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>20.6</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3961,15 +3979,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,C35)+1)/2)/COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -3977,31 +3995,31 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16">
+      <c r="J35" s="30">
         <f>IFERROR((B47/B35)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="30">
         <f>IFERROR((B55/B35)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="30">
         <f>IFERROR((B75/B35)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>39355</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>5021.3</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>22.6</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4009,15 +4027,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,C36)+1)/2)/COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4025,31 +4043,31 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16">
+      <c r="J36" s="30">
         <f>IFERROR((B48/B36)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="30">
         <f>IFERROR((B56/B36)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="30">
         <f>IFERROR((B76/B36)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>39447</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>6138.6</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>27.6</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4057,15 +4075,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,C37)+1)/2)/COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4073,31 +4091,31 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16">
+      <c r="J37" s="30">
         <f>IFERROR((B49/B37)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="30">
         <f>IFERROR((B57/B37)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="30">
         <f>IFERROR((B77/B37)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>39538</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>4734.5</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>20.6</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4105,15 +4123,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,C38)+1)/2)/COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4121,31 +4139,31 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="30">
         <f>IFERROR((B50/B38)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="30">
         <f>IFERROR((B58/B38)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="30">
         <f>IFERROR((B78/B38)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>39629</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>4040.5</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>17.3</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4153,15 +4171,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,C39)+1)/2)/COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4169,31 +4187,31 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16">
+      <c r="J39" s="30">
         <f>IFERROR((B51/B39)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K39" s="16">
+      <c r="K39" s="30">
         <f>IFERROR((B59/B39)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="30">
         <f>IFERROR((B79/B39)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>39721</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>3921.2</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>16.9</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4201,15 +4219,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,C40)+1)/2)/COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4217,31 +4235,31 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16">
+      <c r="J40" s="30">
         <f>IFERROR((B52/B40)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K40" s="16">
+      <c r="K40" s="30">
         <f>IFERROR((B60/B40)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L40" s="16">
+      <c r="L40" s="30">
         <f>IFERROR((B80/B40)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>39813</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>2959.1</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>13</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4249,15 +4267,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,C41)+1)/2)/COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4265,31 +4283,31 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="30">
         <f>IFERROR(B45/B41-1,"")</f>
         <v/>
       </c>
-      <c r="J41" s="16">
+      <c r="J41" s="30">
         <f>IFERROR((B53/B41)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K41" s="16">
+      <c r="K41" s="30">
         <f>IFERROR((B61/B41)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="30">
         <f>IFERROR((B81/B41)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>39903</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>3020.9</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>14.3</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4297,15 +4315,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,C42)+1)/2)/COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4313,31 +4331,31 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16">
+      <c r="I42" s="30">
         <f>IFERROR(B46/B42-1,"")</f>
         <v/>
       </c>
-      <c r="J42" s="16">
+      <c r="J42" s="30">
         <f>IFERROR((B54/B42)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K42" s="16">
+      <c r="K42" s="30">
         <f>IFERROR((B62/B42)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L42" s="16">
+      <c r="L42" s="30">
         <f>IFERROR((B82/B42)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>39994</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>4291.1</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>20</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4345,15 +4363,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,C43)+1)/2)/COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4361,31 +4379,31 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="30">
         <f>IFERROR(B47/B43-1,"")</f>
         <v/>
       </c>
-      <c r="J43" s="16">
+      <c r="J43" s="30">
         <f>IFERROR((B55/B43)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K43" s="16">
+      <c r="K43" s="30">
         <f>IFERROR((B63/B43)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="30">
         <f>IFERROR((B83/B43)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>40086</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>5083.9</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4393,15 +4411,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,C44)+1)/2)/COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4409,31 +4427,31 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16">
+      <c r="I44" s="30">
         <f>IFERROR(B48/B44-1,"")</f>
         <v/>
       </c>
-      <c r="J44" s="16">
+      <c r="J44" s="30">
         <f>IFERROR((B56/B44)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K44" s="16">
+      <c r="K44" s="30">
         <f>IFERROR((B64/B44)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="30">
         <f>IFERROR((B84/B44)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>40178</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>5201</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>23.2</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4441,15 +4459,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E45" s="21">
+      <c r="E45" s="33">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="30">
         <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
         <v/>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="30">
         <f>IF(C45="","",(COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,C45)+1)/2)/COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4457,31 +4475,31 @@
         <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="30">
         <f>IFERROR(B49/B45-1,"")</f>
         <v/>
       </c>
-      <c r="J45" s="16">
+      <c r="J45" s="30">
         <f>IFERROR((B57/B45)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K45" s="16">
+      <c r="K45" s="30">
         <f>IFERROR((B65/B45)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L45" s="16">
+      <c r="L45" s="30">
         <f>IFERROR((B85/B45)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>40268</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>5249.1</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>22.3</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4489,15 +4507,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E46" s="21">
+      <c r="E46" s="33">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="30">
         <f>IF(AND(D46=D42,E42&lt;&gt;""),E46/E42-1,"")</f>
         <v/>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="30">
         <f>IF(C46="","",(COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,C46)+1)/2)/COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4505,31 +4523,31 @@
         <f>IF(G46="","",IF(G46&lt;=20%,"Q1 Cheapest",IF(G46&lt;=40%,"Q2",IF(G46&lt;=60%,"Q3",IF(G46&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="30">
         <f>IFERROR(B50/B46-1,"")</f>
         <v/>
       </c>
-      <c r="J46" s="16">
+      <c r="J46" s="30">
         <f>IFERROR((B58/B46)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K46" s="16">
+      <c r="K46" s="30">
         <f>IFERROR((B66/B46)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L46" s="16">
+      <c r="L46" s="30">
         <f>IFERROR((B86/B46)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>40359</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>5312.5</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>22.3</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -4537,15 +4555,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E47" s="21">
+      <c r="E47" s="33">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="30">
         <f>IF(AND(D47=D43,E43&lt;&gt;""),E47/E43-1,"")</f>
         <v/>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="30">
         <f>IF(C47="","",(COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,C47)+1)/2)/COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4553,31 +4571,31 @@
         <f>IF(G47="","",IF(G47&lt;=20%,"Q1 Cheapest",IF(G47&lt;=40%,"Q2",IF(G47&lt;=60%,"Q3",IF(G47&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="30">
         <f>IFERROR(B51/B47-1,"")</f>
         <v/>
       </c>
-      <c r="J47" s="16">
+      <c r="J47" s="30">
         <f>IFERROR((B59/B47)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K47" s="16">
+      <c r="K47" s="30">
         <f>IFERROR((B67/B47)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L47" s="16">
+      <c r="L47" s="30">
         <f>IFERROR((B87/B47)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>40451</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>6029.9</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>25.5</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4585,15 +4603,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E48" s="21">
+      <c r="E48" s="33">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="30">
         <f>IF(AND(D48=D44,E44&lt;&gt;""),E48/E44-1,"")</f>
         <v/>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="30">
         <f>IF(C48="","",(COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,C48)+1)/2)/COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4601,31 +4619,31 @@
         <f>IF(G48="","",IF(G48&lt;=20%,"Q1 Cheapest",IF(G48&lt;=40%,"Q2",IF(G48&lt;=60%,"Q3",IF(G48&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I48" s="16">
+      <c r="I48" s="30">
         <f>IFERROR(B52/B48-1,"")</f>
         <v/>
       </c>
-      <c r="J48" s="16">
+      <c r="J48" s="30">
         <f>IFERROR((B60/B48)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K48" s="16">
+      <c r="K48" s="30">
         <f>IFERROR((B68/B48)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L48" s="16">
+      <c r="L48" s="30">
         <f>IFERROR((B88/B48)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>40543</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>6134.5</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>24.5</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4633,15 +4651,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E49" s="21">
+      <c r="E49" s="33">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="30">
         <f>IF(AND(D49=D45,E45&lt;&gt;""),E49/E45-1,"")</f>
         <v/>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="30">
         <f>IF(C49="","",(COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,C49)+1)/2)/COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4649,31 +4667,31 @@
         <f>IF(G49="","",IF(G49&lt;=20%,"Q1 Cheapest",IF(G49&lt;=40%,"Q2",IF(G49&lt;=60%,"Q3",IF(G49&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I49" s="16">
+      <c r="I49" s="30">
         <f>IFERROR(B53/B49-1,"")</f>
         <v/>
       </c>
-      <c r="J49" s="16">
+      <c r="J49" s="30">
         <f>IFERROR((B61/B49)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K49" s="16">
+      <c r="K49" s="30">
         <f>IFERROR((B69/B49)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="30">
         <f>IFERROR((B89/B49)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>40633</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>5833.7</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>22.1</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4681,15 +4699,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E50" s="21">
+      <c r="E50" s="33">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="30">
         <f>IF(AND(D50=D46,E46&lt;&gt;""),E50/E46-1,"")</f>
         <v/>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="30">
         <f>IF(C50="","",(COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,C50)+1)/2)/COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4697,31 +4715,31 @@
         <f>IF(G50="","",IF(G50&lt;=20%,"Q1 Cheapest",IF(G50&lt;=40%,"Q2",IF(G50&lt;=60%,"Q3",IF(G50&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="30">
         <f>IFERROR(B54/B50-1,"")</f>
         <v/>
       </c>
-      <c r="J50" s="16">
+      <c r="J50" s="30">
         <f>IFERROR((B62/B50)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="30">
         <f>IFERROR((B70/B50)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L50" s="16">
+      <c r="L50" s="30">
         <f>IFERROR((B90/B50)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>40724</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>5647.4</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>20.8</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4729,15 +4747,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E51" s="21">
+      <c r="E51" s="33">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="30">
         <f>IF(AND(D51=D47,E47&lt;&gt;""),E51/E47-1,"")</f>
         <v/>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="30">
         <f>IF(C51="","",(COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,C51)+1)/2)/COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4745,31 +4763,31 @@
         <f>IF(G51="","",IF(G51&lt;=20%,"Q1 Cheapest",IF(G51&lt;=40%,"Q2",IF(G51&lt;=60%,"Q3",IF(G51&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I51" s="16">
+      <c r="I51" s="30">
         <f>IFERROR(B55/B51-1,"")</f>
         <v/>
       </c>
-      <c r="J51" s="16">
+      <c r="J51" s="30">
         <f>IFERROR((B63/B51)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K51" s="16">
+      <c r="K51" s="30">
         <f>IFERROR((B71/B51)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L51" s="16">
+      <c r="L51" s="30">
         <f>IFERROR((B91/B51)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>40816</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>4943.2</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>17.9</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4777,15 +4795,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="33">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="30">
         <f>IF(AND(D52=D48,E48&lt;&gt;""),E52/E48-1,"")</f>
         <v/>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="30">
         <f>IF(C52="","",(COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,C52)+1)/2)/COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4793,31 +4811,31 @@
         <f>IF(G52="","",IF(G52&lt;=20%,"Q1 Cheapest",IF(G52&lt;=40%,"Q2",IF(G52&lt;=60%,"Q3",IF(G52&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I52" s="16">
+      <c r="I52" s="30">
         <f>IFERROR(B56/B52-1,"")</f>
         <v/>
       </c>
-      <c r="J52" s="16">
+      <c r="J52" s="30">
         <f>IFERROR((B64/B52)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K52" s="16">
+      <c r="K52" s="30">
         <f>IFERROR((B72/B52)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L52" s="16">
+      <c r="L52" s="30">
         <f>IFERROR((B92/B52)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>40908</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>4624.3</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>16.8</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4825,15 +4843,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="33">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="30">
         <f>IF(AND(D53=D49,E49&lt;&gt;""),E53/E49-1,"")</f>
         <v/>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="30">
         <f>IF(C53="","",(COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,C53)+1)/2)/COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4841,31 +4859,31 @@
         <f>IF(G53="","",IF(G53&lt;=20%,"Q1 Cheapest",IF(G53&lt;=40%,"Q2",IF(G53&lt;=60%,"Q3",IF(G53&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I53" s="16">
+      <c r="I53" s="30">
         <f>IFERROR(B57/B53-1,"")</f>
         <v/>
       </c>
-      <c r="J53" s="16">
+      <c r="J53" s="30">
         <f>IFERROR((B65/B53)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="30">
         <f>IFERROR((B73/B53)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L53" s="16">
+      <c r="L53" s="30">
         <f>IFERROR((B93/B53)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>40999</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>5295.5</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>18.7</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4873,15 +4891,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="33">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="30">
         <f>IF(AND(D54=D50,E50&lt;&gt;""),E54/E50-1,"")</f>
         <v/>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="30">
         <f>IF(C54="","",(COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,C54)+1)/2)/COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4889,31 +4907,31 @@
         <f>IF(G54="","",IF(G54&lt;=20%,"Q1 Cheapest",IF(G54&lt;=40%,"Q2",IF(G54&lt;=60%,"Q3",IF(G54&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I54" s="16">
+      <c r="I54" s="30">
         <f>IFERROR(B58/B54-1,"")</f>
         <v/>
       </c>
-      <c r="J54" s="16">
+      <c r="J54" s="30">
         <f>IFERROR((B66/B54)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K54" s="16">
+      <c r="K54" s="30">
         <f>IFERROR((B74/B54)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L54" s="16">
+      <c r="L54" s="30">
         <f>IFERROR((B94/B54)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>41090</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>5278.9</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>17.5</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4921,15 +4939,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E55" s="21">
+      <c r="E55" s="33">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="30">
         <f>IF(AND(D55=D51,E51&lt;&gt;""),E55/E51-1,"")</f>
         <v/>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="30">
         <f>IF(C55="","",(COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,C55)+1)/2)/COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4937,31 +4955,31 @@
         <f>IF(G55="","",IF(G55&lt;=20%,"Q1 Cheapest",IF(G55&lt;=40%,"Q2",IF(G55&lt;=60%,"Q3",IF(G55&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I55" s="16">
+      <c r="I55" s="30">
         <f>IFERROR(B59/B55-1,"")</f>
         <v/>
       </c>
-      <c r="J55" s="16">
+      <c r="J55" s="30">
         <f>IFERROR((B67/B55)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="30">
         <f>IFERROR((B75/B55)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L55" s="16">
+      <c r="L55" s="30">
         <f>IFERROR((B95/B55)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>41182</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>5703.3</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>19.2</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4969,15 +4987,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="33">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="30">
         <f>IF(AND(D56=D52,E52&lt;&gt;""),E56/E52-1,"")</f>
         <v/>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="30">
         <f>IF(C56="","",(COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,C56)+1)/2)/COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -4985,31 +5003,31 @@
         <f>IF(G56="","",IF(G56&lt;=20%,"Q1 Cheapest",IF(G56&lt;=40%,"Q2",IF(G56&lt;=60%,"Q3",IF(G56&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I56" s="16">
+      <c r="I56" s="30">
         <f>IFERROR(B60/B56-1,"")</f>
         <v/>
       </c>
-      <c r="J56" s="16">
+      <c r="J56" s="30">
         <f>IFERROR((B68/B56)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K56" s="16">
+      <c r="K56" s="30">
         <f>IFERROR((B76/B56)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L56" s="16">
+      <c r="L56" s="30">
         <f>IFERROR((B96/B56)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>41274</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>5905.1</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>18.7</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -5017,15 +5035,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E57" s="21">
+      <c r="E57" s="33">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="30">
         <f>IF(AND(D57=D53,E53&lt;&gt;""),E57/E53-1,"")</f>
         <v/>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="30">
         <f>IF(C57="","",(COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,C57)+1)/2)/COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5033,31 +5051,31 @@
         <f>IF(G57="","",IF(G57&lt;=20%,"Q1 Cheapest",IF(G57&lt;=40%,"Q2",IF(G57&lt;=60%,"Q3",IF(G57&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="30">
         <f>IFERROR(B61/B57-1,"")</f>
         <v/>
       </c>
-      <c r="J57" s="16">
+      <c r="J57" s="30">
         <f>IFERROR((B69/B57)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K57" s="16">
+      <c r="K57" s="30">
         <f>IFERROR((B77/B57)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L57" s="16">
+      <c r="L57" s="30">
         <f>IFERROR((B97/B57)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>41364</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>5682.5</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>17.6</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5065,15 +5083,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E58" s="21">
+      <c r="E58" s="33">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="30">
         <f>IF(AND(D58=D54,E54&lt;&gt;""),E58/E54-1,"")</f>
         <v/>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="30">
         <f>IF(C58="","",(COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,C58)+1)/2)/COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5081,31 +5099,31 @@
         <f>IF(G58="","",IF(G58&lt;=20%,"Q1 Cheapest",IF(G58&lt;=40%,"Q2",IF(G58&lt;=60%,"Q3",IF(G58&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I58" s="16">
+      <c r="I58" s="30">
         <f>IFERROR(B62/B58-1,"")</f>
         <v/>
       </c>
-      <c r="J58" s="16">
+      <c r="J58" s="30">
         <f>IFERROR((B70/B58)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K58" s="16">
+      <c r="K58" s="30">
         <f>IFERROR((B78/B58)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L58" s="16">
+      <c r="L58" s="30">
         <f>IFERROR((B98/B58)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>41455</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>5842.2</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>17.8</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5113,15 +5131,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="33">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="30">
         <f>IF(AND(D59=D55,E55&lt;&gt;""),E59/E55-1,"")</f>
         <v/>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="30">
         <f>IF(C59="","",(COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,C59)+1)/2)/COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5129,31 +5147,31 @@
         <f>IF(G59="","",IF(G59&lt;=20%,"Q1 Cheapest",IF(G59&lt;=40%,"Q2",IF(G59&lt;=60%,"Q3",IF(G59&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I59" s="16">
+      <c r="I59" s="30">
         <f>IFERROR(B63/B59-1,"")</f>
         <v/>
       </c>
-      <c r="J59" s="16">
+      <c r="J59" s="30">
         <f>IFERROR((B71/B59)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K59" s="16">
+      <c r="K59" s="30">
         <f>IFERROR((B79/B59)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L59" s="16">
+      <c r="L59" s="30">
         <f>IFERROR((B99/B59)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>41547</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>5735.3</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>16.8</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5161,15 +5179,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E60" s="21">
+      <c r="E60" s="33">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="30">
         <f>IF(AND(D60=D56,E56&lt;&gt;""),E60/E56-1,"")</f>
         <v/>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="30">
         <f>IF(C60="","",(COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C60)+(COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,C60)+1)/2)/COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5177,31 +5195,31 @@
         <f>IF(G60="","",IF(G60&lt;=20%,"Q1 Cheapest",IF(G60&lt;=40%,"Q2",IF(G60&lt;=60%,"Q3",IF(G60&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I60" s="16">
+      <c r="I60" s="30">
         <f>IFERROR(B64/B60-1,"")</f>
         <v/>
       </c>
-      <c r="J60" s="16">
+      <c r="J60" s="30">
         <f>IFERROR((B72/B60)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="30">
         <f>IFERROR((B80/B60)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L60" s="16">
+      <c r="L60" s="30">
         <f>IFERROR((B100/B60)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>41639</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>6304</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>18.7</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5209,15 +5227,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E61" s="21">
+      <c r="E61" s="33">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="30">
         <f>IF(AND(D61=D57,E57&lt;&gt;""),E61/E57-1,"")</f>
         <v/>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="30">
         <f>IF(C61="","",(COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C61)+(COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,C61)+1)/2)/COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5225,31 +5243,31 @@
         <f>IF(G61="","",IF(G61&lt;=20%,"Q1 Cheapest",IF(G61&lt;=40%,"Q2",IF(G61&lt;=60%,"Q3",IF(G61&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="30">
         <f>IFERROR(B65/B61-1,"")</f>
         <v/>
       </c>
-      <c r="J61" s="16">
+      <c r="J61" s="30">
         <f>IFERROR((B73/B61)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K61" s="16">
+      <c r="K61" s="30">
         <f>IFERROR((B81/B61)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L61" s="16">
+      <c r="L61" s="30">
         <f>IFERROR((B101/B61)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>41729</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>6704.2</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>18.9</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5257,15 +5275,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E62" s="21">
+      <c r="E62" s="33">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="30">
         <f>IF(AND(D62=D58,E58&lt;&gt;""),E62/E58-1,"")</f>
         <v/>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="30">
         <f>IF(C62="","",(COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C62)+(COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,C62)+1)/2)/COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5273,31 +5291,31 @@
         <f>IF(G62="","",IF(G62&lt;=20%,"Q1 Cheapest",IF(G62&lt;=40%,"Q2",IF(G62&lt;=60%,"Q3",IF(G62&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I62" s="16">
+      <c r="I62" s="30">
         <f>IFERROR(B66/B62-1,"")</f>
         <v/>
       </c>
-      <c r="J62" s="16">
+      <c r="J62" s="30">
         <f>IFERROR((B74/B62)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K62" s="16">
+      <c r="K62" s="30">
         <f>IFERROR((B82/B62)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L62" s="16">
+      <c r="L62" s="30">
         <f>IFERROR((B102/B62)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>41820</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>7611.3</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>20.6</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5305,15 +5323,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E63" s="21">
+      <c r="E63" s="33">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="30">
         <f>IF(AND(D63=D59,E59&lt;&gt;""),E63/E59-1,"")</f>
         <v/>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="30">
         <f>IF(C63="","",(COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C63)+(COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,C63)+1)/2)/COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5321,31 +5339,31 @@
         <f>IF(G63="","",IF(G63&lt;=20%,"Q1 Cheapest",IF(G63&lt;=40%,"Q2",IF(G63&lt;=60%,"Q3",IF(G63&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="30">
         <f>IFERROR(B67/B63-1,"")</f>
         <v/>
       </c>
-      <c r="J63" s="16">
+      <c r="J63" s="30">
         <f>IFERROR((B75/B63)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K63" s="16">
+      <c r="K63" s="30">
         <f>IFERROR((B83/B63)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L63" s="16">
+      <c r="L63" s="30">
         <f>IFERROR((B103/B63)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>41912</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>7964.8</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>20.8</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5353,15 +5371,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E64" s="21">
+      <c r="E64" s="33">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="30">
         <f>IF(AND(D64=D60,E60&lt;&gt;""),E64/E60-1,"")</f>
         <v/>
       </c>
-      <c r="G64" s="16">
+      <c r="G64" s="30">
         <f>IF(C64="","",(COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C64)+(COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,C64)+1)/2)/COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5369,31 +5387,31 @@
         <f>IF(G64="","",IF(G64&lt;=20%,"Q1 Cheapest",IF(G64&lt;=40%,"Q2",IF(G64&lt;=60%,"Q3",IF(G64&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I64" s="16">
+      <c r="I64" s="30">
         <f>IFERROR(B68/B64-1,"")</f>
         <v/>
       </c>
-      <c r="J64" s="16">
+      <c r="J64" s="30">
         <f>IFERROR((B76/B64)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K64" s="16">
+      <c r="K64" s="30">
         <f>IFERROR((B84/B64)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L64" s="16">
+      <c r="L64" s="30">
         <f>IFERROR((B104/B64)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>42004</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>8282.700000000001</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>21.2</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5401,15 +5419,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E65" s="21">
+      <c r="E65" s="33">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="30">
         <f>IF(AND(D65=D61,E61&lt;&gt;""),E65/E61-1,"")</f>
         <v/>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="30">
         <f>IF(C65="","",(COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C65)+(COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,C65)+1)/2)/COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5417,31 +5435,31 @@
         <f>IF(G65="","",IF(G65&lt;=20%,"Q1 Cheapest",IF(G65&lt;=40%,"Q2",IF(G65&lt;=60%,"Q3",IF(G65&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="30">
         <f>IFERROR(B69/B65-1,"")</f>
         <v/>
       </c>
-      <c r="J65" s="16">
+      <c r="J65" s="30">
         <f>IFERROR((B77/B65)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K65" s="16">
+      <c r="K65" s="30">
         <f>IFERROR((B85/B65)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L65" s="16">
+      <c r="L65" s="30">
         <f>IFERROR((B105/B65)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>42094</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>8491</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>22.7</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -5449,15 +5467,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E66" s="21">
+      <c r="E66" s="33">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="30">
         <f>IF(AND(D66=D62,E62&lt;&gt;""),E66/E62-1,"")</f>
         <v/>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="30">
         <f>IF(C66="","",(COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C66)+(COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,C66)+1)/2)/COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5465,31 +5483,31 @@
         <f>IF(G66="","",IF(G66&lt;=20%,"Q1 Cheapest",IF(G66&lt;=40%,"Q2",IF(G66&lt;=60%,"Q3",IF(G66&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I66" s="16">
+      <c r="I66" s="30">
         <f>IFERROR(B70/B66-1,"")</f>
         <v/>
       </c>
-      <c r="J66" s="16">
+      <c r="J66" s="30">
         <f>IFERROR((B78/B66)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K66" s="16">
+      <c r="K66" s="30">
         <f>IFERROR((B86/B66)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L66" s="16">
+      <c r="L66" s="30">
         <f>IFERROR((B106/B66)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="n">
+      <c r="A67" s="31" t="n">
         <v>42185</v>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B67" s="24" t="n">
         <v>8368.5</v>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="25" t="n">
         <v>23.2</v>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -5497,15 +5515,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E67" s="21">
+      <c r="E67" s="33">
         <f>IFERROR(B67/C67,"")</f>
         <v/>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="30">
         <f>IF(AND(D67=D63,E63&lt;&gt;""),E67/E63-1,"")</f>
         <v/>
       </c>
-      <c r="G67" s="16">
+      <c r="G67" s="30">
         <f>IF(C67="","",(COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C67)+(COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,C67)+1)/2)/COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5513,31 +5531,31 @@
         <f>IF(G67="","",IF(G67&lt;=20%,"Q1 Cheapest",IF(G67&lt;=40%,"Q2",IF(G67&lt;=60%,"Q3",IF(G67&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I67" s="16">
+      <c r="I67" s="30">
         <f>IFERROR(B71/B67-1,"")</f>
         <v/>
       </c>
-      <c r="J67" s="16">
+      <c r="J67" s="30">
         <f>IFERROR((B79/B67)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K67" s="16">
+      <c r="K67" s="30">
         <f>IFERROR((B87/B67)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L67" s="16">
+      <c r="L67" s="30">
         <f>IFERROR((B107/B67)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="n">
+      <c r="A68" s="31" t="n">
         <v>42277</v>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B68" s="24" t="n">
         <v>7948.9</v>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C68" s="25" t="n">
         <v>22.2</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -5545,15 +5563,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E68" s="21">
+      <c r="E68" s="33">
         <f>IFERROR(B68/C68,"")</f>
         <v/>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="30">
         <f>IF(AND(D68=D64,E64&lt;&gt;""),E68/E64-1,"")</f>
         <v/>
       </c>
-      <c r="G68" s="16">
+      <c r="G68" s="30">
         <f>IF(C68="","",(COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C68)+(COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,C68)+1)/2)/COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5561,31 +5579,31 @@
         <f>IF(G68="","",IF(G68&lt;=20%,"Q1 Cheapest",IF(G68&lt;=40%,"Q2",IF(G68&lt;=60%,"Q3",IF(G68&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I68" s="16">
+      <c r="I68" s="30">
         <f>IFERROR(B72/B68-1,"")</f>
         <v/>
       </c>
-      <c r="J68" s="16">
+      <c r="J68" s="30">
         <f>IFERROR((B80/B68)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K68" s="16">
+      <c r="K68" s="30">
         <f>IFERROR((B88/B68)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L68" s="16">
+      <c r="L68" s="30">
         <f>IFERROR((B108/B68)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="n">
+      <c r="A69" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B69" s="24" t="n">
         <v>7946.3</v>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="25" t="n">
         <v>21.5</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -5593,15 +5611,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E69" s="21">
+      <c r="E69" s="33">
         <f>IFERROR(B69/C69,"")</f>
         <v/>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="30">
         <f>IF(AND(D69=D65,E65&lt;&gt;""),E69/E65-1,"")</f>
         <v/>
       </c>
-      <c r="G69" s="16">
+      <c r="G69" s="30">
         <f>IF(C69="","",(COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C69)+(COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,C69)+1)/2)/COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5609,31 +5627,31 @@
         <f>IF(G69="","",IF(G69&lt;=20%,"Q1 Cheapest",IF(G69&lt;=40%,"Q2",IF(G69&lt;=60%,"Q3",IF(G69&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I69" s="16">
+      <c r="I69" s="30">
         <f>IFERROR(B73/B69-1,"")</f>
         <v/>
       </c>
-      <c r="J69" s="16">
+      <c r="J69" s="30">
         <f>IFERROR((B81/B69)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K69" s="16">
+      <c r="K69" s="30">
         <f>IFERROR((B89/B69)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L69" s="16">
+      <c r="L69" s="30">
         <f>IFERROR((B109/B69)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="n">
+      <c r="A70" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B70" s="6" t="n">
+      <c r="B70" s="24" t="n">
         <v>7738.4</v>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C70" s="25" t="n">
         <v>20.9</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -5641,15 +5659,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E70" s="21">
+      <c r="E70" s="33">
         <f>IFERROR(B70/C70,"")</f>
         <v/>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="30">
         <f>IF(AND(D70=D66,E66&lt;&gt;""),E70/E66-1,"")</f>
         <v/>
       </c>
-      <c r="G70" s="16">
+      <c r="G70" s="30">
         <f>IF(C70="","",(COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C70)+(COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,C70)+1)/2)/COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5657,31 +5675,31 @@
         <f>IF(G70="","",IF(G70&lt;=20%,"Q1 Cheapest",IF(G70&lt;=40%,"Q2",IF(G70&lt;=60%,"Q3",IF(G70&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I70" s="16">
+      <c r="I70" s="30">
         <f>IFERROR(B74/B70-1,"")</f>
         <v/>
       </c>
-      <c r="J70" s="16">
+      <c r="J70" s="30">
         <f>IFERROR((B82/B70)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K70" s="16">
+      <c r="K70" s="30">
         <f>IFERROR((B90/B70)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L70" s="16">
+      <c r="L70" s="30">
         <f>IFERROR((B110/B70)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="n">
+      <c r="A71" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B71" s="24" t="n">
         <v>8287.700000000001</v>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C71" s="25" t="n">
         <v>22.8</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -5689,15 +5707,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E71" s="21">
+      <c r="E71" s="33">
         <f>IFERROR(B71/C71,"")</f>
         <v/>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="30">
         <f>IF(AND(D71=D67,E67&lt;&gt;""),E71/E67-1,"")</f>
         <v/>
       </c>
-      <c r="G71" s="16">
+      <c r="G71" s="30">
         <f>IF(C71="","",(COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C71)+(COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,C71)+1)/2)/COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5705,31 +5723,31 @@
         <f>IF(G71="","",IF(G71&lt;=20%,"Q1 Cheapest",IF(G71&lt;=40%,"Q2",IF(G71&lt;=60%,"Q3",IF(G71&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I71" s="16">
+      <c r="I71" s="30">
         <f>IFERROR(B75/B71-1,"")</f>
         <v/>
       </c>
-      <c r="J71" s="16">
+      <c r="J71" s="30">
         <f>IFERROR((B83/B71)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K71" s="16">
+      <c r="K71" s="30">
         <f>IFERROR((B91/B71)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L71" s="16">
+      <c r="L71" s="30">
         <f>IFERROR((B111/B71)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="n">
+      <c r="A72" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B72" s="6" t="n">
+      <c r="B72" s="24" t="n">
         <v>8611.1</v>
       </c>
-      <c r="C72" s="7" t="n">
+      <c r="C72" s="25" t="n">
         <v>23.4</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -5737,15 +5755,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E72" s="21">
+      <c r="E72" s="33">
         <f>IFERROR(B72/C72,"")</f>
         <v/>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="30">
         <f>IF(AND(D72=D68,E68&lt;&gt;""),E72/E68-1,"")</f>
         <v/>
       </c>
-      <c r="G72" s="16">
+      <c r="G72" s="30">
         <f>IF(C72="","",(COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C72)+(COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,C72)+1)/2)/COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5753,28 +5771,28 @@
         <f>IF(G72="","",IF(G72&lt;=20%,"Q1 Cheapest",IF(G72&lt;=40%,"Q2",IF(G72&lt;=60%,"Q3",IF(G72&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I72" s="16">
+      <c r="I72" s="30">
         <f>IFERROR(B76/B72-1,"")</f>
         <v/>
       </c>
-      <c r="J72" s="16">
+      <c r="J72" s="30">
         <f>IFERROR((B84/B72)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K72" s="16">
+      <c r="K72" s="30">
         <f>IFERROR((B92/B72)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L72" s="16" t="n"/>
+      <c r="L72" s="30" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="n">
+      <c r="A73" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B73" s="6" t="n">
+      <c r="B73" s="24" t="n">
         <v>8185.8</v>
       </c>
-      <c r="C73" s="7" t="n">
+      <c r="C73" s="25" t="n">
         <v>21.9</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -5782,15 +5800,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E73" s="21">
+      <c r="E73" s="33">
         <f>IFERROR(B73/C73,"")</f>
         <v/>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="30">
         <f>IF(AND(D73=D69,E69&lt;&gt;""),E73/E69-1,"")</f>
         <v/>
       </c>
-      <c r="G73" s="16">
+      <c r="G73" s="30">
         <f>IF(C73="","",(COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C73)+(COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,C73)+1)/2)/COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5798,28 +5816,28 @@
         <f>IF(G73="","",IF(G73&lt;=20%,"Q1 Cheapest",IF(G73&lt;=40%,"Q2",IF(G73&lt;=60%,"Q3",IF(G73&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I73" s="16">
+      <c r="I73" s="30">
         <f>IFERROR(B77/B73-1,"")</f>
         <v/>
       </c>
-      <c r="J73" s="16">
+      <c r="J73" s="30">
         <f>IFERROR((B85/B73)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K73" s="16">
+      <c r="K73" s="30">
         <f>IFERROR((B93/B73)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L73" s="16" t="n"/>
+      <c r="L73" s="30" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="n">
+      <c r="A74" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B74" s="6" t="n">
+      <c r="B74" s="24" t="n">
         <v>9173.700000000001</v>
       </c>
-      <c r="C74" s="7" t="n">
+      <c r="C74" s="25" t="n">
         <v>23.3</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5827,15 +5845,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E74" s="21">
+      <c r="E74" s="33">
         <f>IFERROR(B74/C74,"")</f>
         <v/>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="30">
         <f>IF(AND(D74=D70,E70&lt;&gt;""),E74/E70-1,"")</f>
         <v/>
       </c>
-      <c r="G74" s="16">
+      <c r="G74" s="30">
         <f>IF(C74="","",(COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C74)+(COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,C74)+1)/2)/COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5843,28 +5861,28 @@
         <f>IF(G74="","",IF(G74&lt;=20%,"Q1 Cheapest",IF(G74&lt;=40%,"Q2",IF(G74&lt;=60%,"Q3",IF(G74&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I74" s="16">
+      <c r="I74" s="30">
         <f>IFERROR(B78/B74-1,"")</f>
         <v/>
       </c>
-      <c r="J74" s="16">
+      <c r="J74" s="30">
         <f>IFERROR((B86/B74)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K74" s="16">
+      <c r="K74" s="30">
         <f>IFERROR((B94/B74)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L74" s="16" t="n"/>
+      <c r="L74" s="30" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="n">
+      <c r="A75" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="24" t="n">
         <v>9520.9</v>
       </c>
-      <c r="C75" s="7" t="n">
+      <c r="C75" s="25" t="n">
         <v>24.2</v>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5872,15 +5890,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E75" s="21">
+      <c r="E75" s="33">
         <f>IFERROR(B75/C75,"")</f>
         <v/>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="30">
         <f>IF(AND(D75=D71,E71&lt;&gt;""),E75/E71-1,"")</f>
         <v/>
       </c>
-      <c r="G75" s="16">
+      <c r="G75" s="30">
         <f>IF(C75="","",(COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C75)+(COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,C75)+1)/2)/COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5888,28 +5906,28 @@
         <f>IF(G75="","",IF(G75&lt;=20%,"Q1 Cheapest",IF(G75&lt;=40%,"Q2",IF(G75&lt;=60%,"Q3",IF(G75&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I75" s="16">
+      <c r="I75" s="30">
         <f>IFERROR(B79/B75-1,"")</f>
         <v/>
       </c>
-      <c r="J75" s="16">
+      <c r="J75" s="30">
         <f>IFERROR((B87/B75)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K75" s="16">
+      <c r="K75" s="30">
         <f>IFERROR((B95/B75)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L75" s="16" t="n"/>
+      <c r="L75" s="30" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="n">
+      <c r="A76" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B76" s="6" t="n">
+      <c r="B76" s="24" t="n">
         <v>9788.6</v>
       </c>
-      <c r="C76" s="7" t="n">
+      <c r="C76" s="25" t="n">
         <v>25.4</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5917,15 +5935,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E76" s="21">
+      <c r="E76" s="33">
         <f>IFERROR(B76/C76,"")</f>
         <v/>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="30">
         <f>IF(AND(D76=D72,E72&lt;&gt;""),E76/E72-1,"")</f>
         <v/>
       </c>
-      <c r="G76" s="16">
+      <c r="G76" s="30">
         <f>IF(C76="","",(COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C76)+(COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,C76)+1)/2)/COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5933,28 +5951,28 @@
         <f>IF(G76="","",IF(G76&lt;=20%,"Q1 Cheapest",IF(G76&lt;=40%,"Q2",IF(G76&lt;=60%,"Q3",IF(G76&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I76" s="16">
+      <c r="I76" s="30">
         <f>IFERROR(B80/B76-1,"")</f>
         <v/>
       </c>
-      <c r="J76" s="16">
+      <c r="J76" s="30">
         <f>IFERROR((B88/B76)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K76" s="16">
+      <c r="K76" s="30">
         <f>IFERROR((B96/B76)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L76" s="16" t="n"/>
+      <c r="L76" s="30" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="n">
+      <c r="A77" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="24" t="n">
         <v>10530</v>
       </c>
-      <c r="C77" s="7" t="n">
+      <c r="C77" s="25" t="n">
         <v>26.9</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5962,15 +5980,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E77" s="21">
+      <c r="E77" s="33">
         <f>IFERROR(B77/C77,"")</f>
         <v/>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="30">
         <f>IF(AND(D77=D73,E73&lt;&gt;""),E77/E73-1,"")</f>
         <v/>
       </c>
-      <c r="G77" s="16">
+      <c r="G77" s="30">
         <f>IF(C77="","",(COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C77)+(COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,C77)+1)/2)/COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -5978,28 +5996,28 @@
         <f>IF(G77="","",IF(G77&lt;=20%,"Q1 Cheapest",IF(G77&lt;=40%,"Q2",IF(G77&lt;=60%,"Q3",IF(G77&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I77" s="16">
+      <c r="I77" s="30">
         <f>IFERROR(B81/B77-1,"")</f>
         <v/>
       </c>
-      <c r="J77" s="16">
+      <c r="J77" s="30">
         <f>IFERROR((B89/B77)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K77" s="16">
+      <c r="K77" s="30">
         <f>IFERROR((B97/B77)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L77" s="16" t="n"/>
+      <c r="L77" s="30" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="n">
+      <c r="A78" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B78" s="6" t="n">
+      <c r="B78" s="24" t="n">
         <v>10113.7</v>
       </c>
-      <c r="C78" s="7" t="n">
+      <c r="C78" s="25" t="n">
         <v>24.7</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6007,15 +6025,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E78" s="21">
+      <c r="E78" s="33">
         <f>IFERROR(B78/C78,"")</f>
         <v/>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="30">
         <f>IF(AND(D78=D74,E74&lt;&gt;""),E78/E74-1,"")</f>
         <v/>
       </c>
-      <c r="G78" s="16">
+      <c r="G78" s="30">
         <f>IF(C78="","",(COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C78)+(COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,C78)+1)/2)/COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6023,28 +6041,28 @@
         <f>IF(G78="","",IF(G78&lt;=20%,"Q1 Cheapest",IF(G78&lt;=40%,"Q2",IF(G78&lt;=60%,"Q3",IF(G78&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I78" s="16">
+      <c r="I78" s="30">
         <f>IFERROR(B82/B78-1,"")</f>
         <v/>
       </c>
-      <c r="J78" s="16">
+      <c r="J78" s="30">
         <f>IFERROR((B90/B78)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K78" s="16">
+      <c r="K78" s="30">
         <f>IFERROR((B98/B78)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L78" s="16" t="n"/>
+      <c r="L78" s="30" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="n">
+      <c r="A79" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="24" t="n">
         <v>10714.3</v>
       </c>
-      <c r="C79" s="7" t="n">
+      <c r="C79" s="25" t="n">
         <v>25.9</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6052,15 +6070,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E79" s="21">
+      <c r="E79" s="33">
         <f>IFERROR(B79/C79,"")</f>
         <v/>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="30">
         <f>IF(AND(D79=D75,E75&lt;&gt;""),E79/E75-1,"")</f>
         <v/>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="30">
         <f>IF(C79="","",(COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C79)+(COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,C79)+1)/2)/COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6068,28 +6086,28 @@
         <f>IF(G79="","",IF(G79&lt;=20%,"Q1 Cheapest",IF(G79&lt;=40%,"Q2",IF(G79&lt;=60%,"Q3",IF(G79&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I79" s="16">
+      <c r="I79" s="30">
         <f>IFERROR(B83/B79-1,"")</f>
         <v/>
       </c>
-      <c r="J79" s="16">
+      <c r="J79" s="30">
         <f>IFERROR((B91/B79)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K79" s="16">
+      <c r="K79" s="30">
         <f>IFERROR((B99/B79)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L79" s="16" t="n"/>
+      <c r="L79" s="30" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="18" t="n">
+      <c r="A80" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B80" s="24" t="n">
         <v>10930.45</v>
       </c>
-      <c r="C80" s="7" t="n">
+      <c r="C80" s="25" t="n">
         <v>26.4</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6097,15 +6115,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E80" s="21">
+      <c r="E80" s="33">
         <f>IFERROR(B80/C80,"")</f>
         <v/>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="30">
         <f>IF(AND(D80=D76,E76&lt;&gt;""),E80/E76-1,"")</f>
         <v/>
       </c>
-      <c r="G80" s="16">
+      <c r="G80" s="30">
         <f>IF(C80="","",(COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C80)+(COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,C80)+1)/2)/COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6113,28 +6131,28 @@
         <f>IF(G80="","",IF(G80&lt;=20%,"Q1 Cheapest",IF(G80&lt;=40%,"Q2",IF(G80&lt;=60%,"Q3",IF(G80&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I80" s="16">
+      <c r="I80" s="30">
         <f>IFERROR(B84/B80-1,"")</f>
         <v/>
       </c>
-      <c r="J80" s="16">
+      <c r="J80" s="30">
         <f>IFERROR((B92/B80)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K80" s="16">
+      <c r="K80" s="30">
         <f>IFERROR((B100/B80)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L80" s="16" t="n"/>
+      <c r="L80" s="30" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="n">
+      <c r="A81" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B81" s="6" t="n">
+      <c r="B81" s="24" t="n">
         <v>10862.55</v>
       </c>
-      <c r="C81" s="7" t="n">
+      <c r="C81" s="25" t="n">
         <v>26.2</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6142,15 +6160,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E81" s="21">
+      <c r="E81" s="33">
         <f>IFERROR(B81/C81,"")</f>
         <v/>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="30">
         <f>IF(AND(D81=D77,E77&lt;&gt;""),E81/E77-1,"")</f>
         <v/>
       </c>
-      <c r="G81" s="16">
+      <c r="G81" s="30">
         <f>IF(C81="","",(COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C81)+(COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,C81)+1)/2)/COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6158,28 +6176,28 @@
         <f>IF(G81="","",IF(G81&lt;=20%,"Q1 Cheapest",IF(G81&lt;=40%,"Q2",IF(G81&lt;=60%,"Q3",IF(G81&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I81" s="16">
+      <c r="I81" s="30">
         <f>IFERROR(B85/B81-1,"")</f>
         <v/>
       </c>
-      <c r="J81" s="16">
+      <c r="J81" s="30">
         <f>IFERROR((B93/B81)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K81" s="16">
+      <c r="K81" s="30">
         <f>IFERROR((B101/B81)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L81" s="16" t="n"/>
+      <c r="L81" s="30" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="n">
+      <c r="A82" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B82" s="6" t="n">
+      <c r="B82" s="24" t="n">
         <v>11623.9</v>
       </c>
-      <c r="C82" s="7" t="n">
+      <c r="C82" s="25" t="n">
         <v>29</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6187,15 +6205,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E82" s="21">
+      <c r="E82" s="33">
         <f>IFERROR(B82/C82,"")</f>
         <v/>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="30">
         <f>IF(AND(D82=D78,E78&lt;&gt;""),E82/E78-1,"")</f>
         <v/>
       </c>
-      <c r="G82" s="16">
+      <c r="G82" s="30">
         <f>IF(C82="","",(COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C82)+(COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,C82)+1)/2)/COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6203,28 +6221,28 @@
         <f>IF(G82="","",IF(G82&lt;=20%,"Q1 Cheapest",IF(G82&lt;=40%,"Q2",IF(G82&lt;=60%,"Q3",IF(G82&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I82" s="16">
+      <c r="I82" s="30">
         <f>IFERROR(B86/B82-1,"")</f>
         <v/>
       </c>
-      <c r="J82" s="16">
+      <c r="J82" s="30">
         <f>IFERROR((B94/B82)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K82" s="16">
+      <c r="K82" s="30">
         <f>IFERROR((B102/B82)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L82" s="16" t="n"/>
+      <c r="L82" s="30" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="n">
+      <c r="A83" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B83" s="24" t="n">
         <v>11788.85</v>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="25" t="n">
         <v>29</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6232,15 +6250,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E83" s="21">
+      <c r="E83" s="33">
         <f>IFERROR(B83/C83,"")</f>
         <v/>
       </c>
-      <c r="F83" s="16">
+      <c r="F83" s="30">
         <f>IF(AND(D83=D79,E79&lt;&gt;""),E83/E79-1,"")</f>
         <v/>
       </c>
-      <c r="G83" s="16">
+      <c r="G83" s="30">
         <f>IF(C83="","",(COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C83)+(COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,C83)+1)/2)/COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6248,28 +6266,28 @@
         <f>IF(G83="","",IF(G83&lt;=20%,"Q1 Cheapest",IF(G83&lt;=40%,"Q2",IF(G83&lt;=60%,"Q3",IF(G83&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I83" s="16">
+      <c r="I83" s="30">
         <f>IFERROR(B87/B83-1,"")</f>
         <v/>
       </c>
-      <c r="J83" s="16">
+      <c r="J83" s="30">
         <f>IFERROR((B95/B83)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K83" s="16">
+      <c r="K83" s="30">
         <f>IFERROR((B103/B83)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L83" s="16" t="n"/>
+      <c r="L83" s="30" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="n">
+      <c r="A84" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B84" s="6" t="n">
+      <c r="B84" s="24" t="n">
         <v>11474.45</v>
       </c>
-      <c r="C84" s="7" t="n">
+      <c r="C84" s="25" t="n">
         <v>26.4</v>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6277,15 +6295,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E84" s="21">
+      <c r="E84" s="33">
         <f>IFERROR(B84/C84,"")</f>
         <v/>
       </c>
-      <c r="F84" s="16">
+      <c r="F84" s="30">
         <f>IF(AND(D84=D80,E80&lt;&gt;""),E84/E80-1,"")</f>
         <v/>
       </c>
-      <c r="G84" s="16">
+      <c r="G84" s="30">
         <f>IF(C84="","",(COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C84)+(COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,C84)+1)/2)/COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6293,28 +6311,28 @@
         <f>IF(G84="","",IF(G84&lt;=20%,"Q1 Cheapest",IF(G84&lt;=40%,"Q2",IF(G84&lt;=60%,"Q3",IF(G84&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I84" s="16">
+      <c r="I84" s="30">
         <f>IFERROR(B88/B84-1,"")</f>
         <v/>
       </c>
-      <c r="J84" s="16">
+      <c r="J84" s="30">
         <f>IFERROR((B96/B84)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K84" s="16">
+      <c r="K84" s="30">
         <f>IFERROR((B104/B84)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L84" s="16" t="n"/>
+      <c r="L84" s="30" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="n">
+      <c r="A85" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B85" s="6" t="n">
+      <c r="B85" s="24" t="n">
         <v>12168.45</v>
       </c>
-      <c r="C85" s="7" t="n">
+      <c r="C85" s="25" t="n">
         <v>28.3</v>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -6322,15 +6340,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E85" s="21">
+      <c r="E85" s="33">
         <f>IFERROR(B85/C85,"")</f>
         <v/>
       </c>
-      <c r="F85" s="16">
+      <c r="F85" s="30">
         <f>IF(AND(D85=D81,E81&lt;&gt;""),E85/E81-1,"")</f>
         <v/>
       </c>
-      <c r="G85" s="16">
+      <c r="G85" s="30">
         <f>IF(C85="","",(COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C85)+(COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,C85)+1)/2)/COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6338,28 +6356,28 @@
         <f>IF(G85="","",IF(G85&lt;=20%,"Q1 Cheapest",IF(G85&lt;=40%,"Q2",IF(G85&lt;=60%,"Q3",IF(G85&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I85" s="16">
+      <c r="I85" s="30">
         <f>IFERROR(B89/B85-1,"")</f>
         <v/>
       </c>
-      <c r="J85" s="16">
+      <c r="J85" s="30">
         <f>IFERROR((B97/B85)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K85" s="16">
+      <c r="K85" s="30">
         <f>IFERROR((B105/B85)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L85" s="16" t="n"/>
+      <c r="L85" s="30" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="18" t="n">
+      <c r="A86" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="24" t="n">
         <v>8597.75</v>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C86" s="25" t="n">
         <v>19.4</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -6367,15 +6385,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E86" s="21">
+      <c r="E86" s="33">
         <f>IFERROR(B86/C86,"")</f>
         <v/>
       </c>
-      <c r="F86" s="16">
+      <c r="F86" s="30">
         <f>IF(AND(D86=D82,E82&lt;&gt;""),E86/E82-1,"")</f>
         <v/>
       </c>
-      <c r="G86" s="16">
+      <c r="G86" s="30">
         <f>IF(C86="","",(COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C86)+(COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,C86)+1)/2)/COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6383,28 +6401,28 @@
         <f>IF(G86="","",IF(G86&lt;=20%,"Q1 Cheapest",IF(G86&lt;=40%,"Q2",IF(G86&lt;=60%,"Q3",IF(G86&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I86" s="16">
+      <c r="I86" s="30">
         <f>IFERROR(B90/B86-1,"")</f>
         <v/>
       </c>
-      <c r="J86" s="16">
+      <c r="J86" s="30">
         <f>IFERROR((B98/B86)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K86" s="16">
+      <c r="K86" s="30">
         <f>IFERROR((B106/B86)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L86" s="16" t="n"/>
+      <c r="L86" s="30" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="n">
+      <c r="A87" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="24" t="n">
         <v>10302.1</v>
       </c>
-      <c r="C87" s="7" t="n">
+      <c r="C87" s="25" t="n">
         <v>26.3</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -6412,15 +6430,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E87" s="21">
+      <c r="E87" s="33">
         <f>IFERROR(B87/C87,"")</f>
         <v/>
       </c>
-      <c r="F87" s="16">
+      <c r="F87" s="30">
         <f>IF(AND(D87=D83,E83&lt;&gt;""),E87/E83-1,"")</f>
         <v/>
       </c>
-      <c r="G87" s="16">
+      <c r="G87" s="30">
         <f>IF(C87="","",(COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C87)+(COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,C87)+1)/2)/COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6428,28 +6446,28 @@
         <f>IF(G87="","",IF(G87&lt;=20%,"Q1 Cheapest",IF(G87&lt;=40%,"Q2",IF(G87&lt;=60%,"Q3",IF(G87&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I87" s="16">
+      <c r="I87" s="30">
         <f>IFERROR(B91/B87-1,"")</f>
         <v/>
       </c>
-      <c r="J87" s="16">
+      <c r="J87" s="30">
         <f>IFERROR((B99/B87)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K87" s="16">
+      <c r="K87" s="30">
         <f>IFERROR((B107/B87)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L87" s="16" t="n"/>
+      <c r="L87" s="30" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="n">
+      <c r="A88" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B88" s="6" t="n">
+      <c r="B88" s="24" t="n">
         <v>11247.55</v>
       </c>
-      <c r="C88" s="7" t="n">
+      <c r="C88" s="25" t="n">
         <v>32.7</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6457,15 +6475,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E88" s="21">
+      <c r="E88" s="33">
         <f>IFERROR(B88/C88,"")</f>
         <v/>
       </c>
-      <c r="F88" s="16">
+      <c r="F88" s="30">
         <f>IF(AND(D88=D84,E84&lt;&gt;""),E88/E84-1,"")</f>
         <v/>
       </c>
-      <c r="G88" s="16">
+      <c r="G88" s="30">
         <f>IF(C88="","",(COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C88)+(COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,C88)+1)/2)/COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6473,28 +6491,28 @@
         <f>IF(G88="","",IF(G88&lt;=20%,"Q1 Cheapest",IF(G88&lt;=40%,"Q2",IF(G88&lt;=60%,"Q3",IF(G88&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I88" s="16">
+      <c r="I88" s="30">
         <f>IFERROR(B92/B88-1,"")</f>
         <v/>
       </c>
-      <c r="J88" s="16">
+      <c r="J88" s="30">
         <f>IFERROR((B100/B88)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K88" s="16">
+      <c r="K88" s="30">
         <f>IFERROR((B108/B88)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L88" s="16" t="n"/>
+      <c r="L88" s="30" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="n">
+      <c r="A89" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B89" s="6" t="n">
+      <c r="B89" s="24" t="n">
         <v>13981.75</v>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C89" s="25" t="n">
         <v>38.5</v>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -6502,15 +6520,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E89" s="21">
+      <c r="E89" s="33">
         <f>IFERROR(B89/C89,"")</f>
         <v/>
       </c>
-      <c r="F89" s="16">
+      <c r="F89" s="30">
         <f>IF(AND(D89=D85,E85&lt;&gt;""),E89/E85-1,"")</f>
         <v/>
       </c>
-      <c r="G89" s="16">
+      <c r="G89" s="30">
         <f>IF(C89="","",(COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C89)+(COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,C89)+1)/2)/COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6518,28 +6536,28 @@
         <f>IF(G89="","",IF(G89&lt;=20%,"Q1 Cheapest",IF(G89&lt;=40%,"Q2",IF(G89&lt;=60%,"Q3",IF(G89&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I89" s="16">
+      <c r="I89" s="30">
         <f>IFERROR(B93/B89-1,"")</f>
         <v/>
       </c>
-      <c r="J89" s="16">
+      <c r="J89" s="30">
         <f>IFERROR((B101/B89)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K89" s="16">
+      <c r="K89" s="30">
         <f>IFERROR((B109/B89)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L89" s="16" t="n"/>
+      <c r="L89" s="30" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="n">
+      <c r="A90" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B90" s="6" t="n">
+      <c r="B90" s="24" t="n">
         <v>14690.7</v>
       </c>
-      <c r="C90" s="7" t="n">
+      <c r="C90" s="25" t="n">
         <v>33.2</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6547,15 +6565,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E90" s="21">
+      <c r="E90" s="33">
         <f>IFERROR(B90/C90,"")</f>
         <v/>
       </c>
-      <c r="F90" s="16">
+      <c r="F90" s="30">
         <f>IF(AND(D90=D86,E86&lt;&gt;""),E90/E86-1,"")</f>
         <v/>
       </c>
-      <c r="G90" s="16">
+      <c r="G90" s="30">
         <f>IF(C90="","",(COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C90)+(COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,C90)+1)/2)/COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6563,28 +6581,28 @@
         <f>IF(G90="","",IF(G90&lt;=20%,"Q1 Cheapest",IF(G90&lt;=40%,"Q2",IF(G90&lt;=60%,"Q3",IF(G90&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I90" s="16">
+      <c r="I90" s="30">
         <f>IFERROR(B94/B90-1,"")</f>
         <v/>
       </c>
-      <c r="J90" s="16">
+      <c r="J90" s="30">
         <f>IFERROR((B102/B90)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K90" s="16">
+      <c r="K90" s="30">
         <f>IFERROR((B110/B90)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L90" s="16" t="n"/>
+      <c r="L90" s="30" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="n">
+      <c r="A91" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B91" s="6" t="n">
+      <c r="B91" s="24" t="n">
         <v>15721.5</v>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="25" t="n">
         <v>28.3</v>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -6592,15 +6610,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E91" s="21">
+      <c r="E91" s="33">
         <f>IFERROR(B91/C91,"")</f>
         <v/>
       </c>
-      <c r="F91" s="16">
+      <c r="F91" s="30">
         <f>IF(AND(D91=D87,E87&lt;&gt;""),E91/E87-1,"")</f>
         <v/>
       </c>
-      <c r="G91" s="16">
+      <c r="G91" s="30">
         <f>IF(C91="","",(COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C91)+(COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,C91)+1)/2)/COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6608,28 +6626,28 @@
         <f>IF(G91="","",IF(G91&lt;=20%,"Q1 Cheapest",IF(G91&lt;=40%,"Q2",IF(G91&lt;=60%,"Q3",IF(G91&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I91" s="16">
+      <c r="I91" s="30">
         <f>IFERROR(B95/B91-1,"")</f>
         <v/>
       </c>
-      <c r="J91" s="16">
+      <c r="J91" s="30">
         <f>IFERROR((B103/B91)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K91" s="16">
+      <c r="K91" s="30">
         <f>IFERROR((B111/B91)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L91" s="16" t="n"/>
+      <c r="L91" s="30" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="n">
+      <c r="A92" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B92" s="24" t="n">
         <v>17618.15</v>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C92" s="25" t="n">
         <v>27</v>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6637,15 +6655,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E92" s="21">
+      <c r="E92" s="33">
         <f>IFERROR(B92/C92,"")</f>
         <v/>
       </c>
-      <c r="F92" s="16">
+      <c r="F92" s="30">
         <f>IF(AND(D92=D88,E88&lt;&gt;""),E92/E88-1,"")</f>
         <v/>
       </c>
-      <c r="G92" s="16">
+      <c r="G92" s="30">
         <f>IF(C92="","",(COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C92)+(COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,C92)+1)/2)/COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6653,25 +6671,25 @@
         <f>IF(G92="","",IF(G92&lt;=20%,"Q1 Cheapest",IF(G92&lt;=40%,"Q2",IF(G92&lt;=60%,"Q3",IF(G92&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I92" s="16">
+      <c r="I92" s="30">
         <f>IFERROR(B96/B92-1,"")</f>
         <v/>
       </c>
-      <c r="J92" s="16">
+      <c r="J92" s="30">
         <f>IFERROR((B104/B92)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K92" s="16" t="n"/>
-      <c r="L92" s="16" t="n"/>
+      <c r="K92" s="30" t="n"/>
+      <c r="L92" s="30" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="18" t="n">
+      <c r="A93" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B93" s="24" t="n">
         <v>17354.05</v>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C93" s="25" t="n">
         <v>24.1</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -6679,15 +6697,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E93" s="21">
+      <c r="E93" s="33">
         <f>IFERROR(B93/C93,"")</f>
         <v/>
       </c>
-      <c r="F93" s="16">
+      <c r="F93" s="30">
         <f>IF(AND(D93=D89,E89&lt;&gt;""),E93/E89-1,"")</f>
         <v/>
       </c>
-      <c r="G93" s="16">
+      <c r="G93" s="30">
         <f>IF(C93="","",(COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C93)+(COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,C93)+1)/2)/COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6695,25 +6713,25 @@
         <f>IF(G93="","",IF(G93&lt;=20%,"Q1 Cheapest",IF(G93&lt;=40%,"Q2",IF(G93&lt;=60%,"Q3",IF(G93&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I93" s="16">
+      <c r="I93" s="30">
         <f>IFERROR(B97/B93-1,"")</f>
         <v/>
       </c>
-      <c r="J93" s="16">
+      <c r="J93" s="30">
         <f>IFERROR((B105/B93)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K93" s="16" t="n"/>
-      <c r="L93" s="16" t="n"/>
+      <c r="K93" s="30" t="n"/>
+      <c r="L93" s="30" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="18" t="n">
+      <c r="A94" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B94" s="24" t="n">
         <v>17464.75</v>
       </c>
-      <c r="C94" s="7" t="n">
+      <c r="C94" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -6721,15 +6739,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E94" s="21">
+      <c r="E94" s="33">
         <f>IFERROR(B94/C94,"")</f>
         <v/>
       </c>
-      <c r="F94" s="16">
+      <c r="F94" s="30">
         <f>IF(AND(D94=D90,E90&lt;&gt;""),E94/E90-1,"")</f>
         <v/>
       </c>
-      <c r="G94" s="16">
+      <c r="G94" s="30">
         <f>IF(C94="","",(COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C94)+(COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,C94)+1)/2)/COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6737,25 +6755,25 @@
         <f>IF(G94="","",IF(G94&lt;=20%,"Q1 Cheapest",IF(G94&lt;=40%,"Q2",IF(G94&lt;=60%,"Q3",IF(G94&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I94" s="16">
+      <c r="I94" s="30">
         <f>IFERROR(B98/B94-1,"")</f>
         <v/>
       </c>
-      <c r="J94" s="16">
+      <c r="J94" s="30">
         <f>IFERROR((B106/B94)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K94" s="16" t="n"/>
-      <c r="L94" s="16" t="n"/>
+      <c r="K94" s="30" t="n"/>
+      <c r="L94" s="30" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="18" t="n">
+      <c r="A95" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B95" s="6" t="n">
+      <c r="B95" s="24" t="n">
         <v>15780.25</v>
       </c>
-      <c r="C95" s="7" t="n">
+      <c r="C95" s="25" t="n">
         <v>19.5</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6763,15 +6781,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E95" s="21">
+      <c r="E95" s="33">
         <f>IFERROR(B95/C95,"")</f>
         <v/>
       </c>
-      <c r="F95" s="16">
+      <c r="F95" s="30">
         <f>IF(AND(D95=D91,E91&lt;&gt;""),E95/E91-1,"")</f>
         <v/>
       </c>
-      <c r="G95" s="16">
+      <c r="G95" s="30">
         <f>IF(C95="","",(COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C95)+(COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,C95)+1)/2)/COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6779,25 +6797,25 @@
         <f>IF(G95="","",IF(G95&lt;=20%,"Q1 Cheapest",IF(G95&lt;=40%,"Q2",IF(G95&lt;=60%,"Q3",IF(G95&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I95" s="16">
+      <c r="I95" s="30">
         <f>IFERROR(B99/B95-1,"")</f>
         <v/>
       </c>
-      <c r="J95" s="16">
+      <c r="J95" s="30">
         <f>IFERROR((B107/B95)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K95" s="16" t="n"/>
-      <c r="L95" s="16" t="n"/>
+      <c r="K95" s="30" t="n"/>
+      <c r="L95" s="30" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="18" t="n">
+      <c r="A96" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B96" s="6" t="n">
+      <c r="B96" s="24" t="n">
         <v>17094.35</v>
       </c>
-      <c r="C96" s="7" t="n">
+      <c r="C96" s="25" t="n">
         <v>20.6</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6805,15 +6823,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E96" s="21">
+      <c r="E96" s="33">
         <f>IFERROR(B96/C96,"")</f>
         <v/>
       </c>
-      <c r="F96" s="16">
+      <c r="F96" s="30">
         <f>IF(AND(D96=D92,E92&lt;&gt;""),E96/E92-1,"")</f>
         <v/>
       </c>
-      <c r="G96" s="16">
+      <c r="G96" s="30">
         <f>IF(C96="","",(COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C96)+(COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,C96)+1)/2)/COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6821,25 +6839,25 @@
         <f>IF(G96="","",IF(G96&lt;=20%,"Q1 Cheapest",IF(G96&lt;=40%,"Q2",IF(G96&lt;=60%,"Q3",IF(G96&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I96" s="16">
+      <c r="I96" s="30">
         <f>IFERROR(B100/B96-1,"")</f>
         <v/>
       </c>
-      <c r="J96" s="16">
+      <c r="J96" s="30">
         <f>IFERROR((B108/B96)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K96" s="16" t="n"/>
-      <c r="L96" s="16" t="n"/>
+      <c r="K96" s="30" t="n"/>
+      <c r="L96" s="30" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="18" t="n">
+      <c r="A97" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B97" s="6" t="n">
+      <c r="B97" s="24" t="n">
         <v>18105.3</v>
       </c>
-      <c r="C97" s="7" t="n">
+      <c r="C97" s="25" t="n">
         <v>21.8</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -6847,15 +6865,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E97" s="21">
+      <c r="E97" s="33">
         <f>IFERROR(B97/C97,"")</f>
         <v/>
       </c>
-      <c r="F97" s="16">
+      <c r="F97" s="30">
         <f>IF(AND(D97=D93,E93&lt;&gt;""),E97/E93-1,"")</f>
         <v/>
       </c>
-      <c r="G97" s="16">
+      <c r="G97" s="30">
         <f>IF(C97="","",(COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C97)+(COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,C97)+1)/2)/COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6863,25 +6881,25 @@
         <f>IF(G97="","",IF(G97&lt;=20%,"Q1 Cheapest",IF(G97&lt;=40%,"Q2",IF(G97&lt;=60%,"Q3",IF(G97&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I97" s="16">
+      <c r="I97" s="30">
         <f>IFERROR(B101/B97-1,"")</f>
         <v/>
       </c>
-      <c r="J97" s="16">
+      <c r="J97" s="30">
         <f>IFERROR((B109/B97)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K97" s="16" t="n"/>
-      <c r="L97" s="16" t="n"/>
+      <c r="K97" s="30" t="n"/>
+      <c r="L97" s="30" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="18" t="n">
+      <c r="A98" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B98" s="6" t="n">
+      <c r="B98" s="24" t="n">
         <v>17359.75</v>
       </c>
-      <c r="C98" s="7" t="n">
+      <c r="C98" s="25" t="n">
         <v>20.4</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6889,15 +6907,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E98" s="21">
+      <c r="E98" s="33">
         <f>IFERROR(B98/C98,"")</f>
         <v/>
       </c>
-      <c r="F98" s="16">
+      <c r="F98" s="30">
         <f>IF(AND(D98=D94,E94&lt;&gt;""),E98/E94-1,"")</f>
         <v/>
       </c>
-      <c r="G98" s="16">
+      <c r="G98" s="30">
         <f>IF(C98="","",(COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C98)+(COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,C98)+1)/2)/COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6905,25 +6923,25 @@
         <f>IF(G98="","",IF(G98&lt;=20%,"Q1 Cheapest",IF(G98&lt;=40%,"Q2",IF(G98&lt;=60%,"Q3",IF(G98&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I98" s="16">
+      <c r="I98" s="30">
         <f>IFERROR(B102/B98-1,"")</f>
         <v/>
       </c>
-      <c r="J98" s="16">
+      <c r="J98" s="30">
         <f>IFERROR((B110/B98)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K98" s="16" t="n"/>
-      <c r="L98" s="16" t="n"/>
+      <c r="K98" s="30" t="n"/>
+      <c r="L98" s="30" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="18" t="n">
+      <c r="A99" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B99" s="6" t="n">
+      <c r="B99" s="24" t="n">
         <v>19189.05</v>
       </c>
-      <c r="C99" s="7" t="n">
+      <c r="C99" s="25" t="n">
         <v>22.4</v>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6931,15 +6949,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E99" s="21">
+      <c r="E99" s="33">
         <f>IFERROR(B99/C99,"")</f>
         <v/>
       </c>
-      <c r="F99" s="16">
+      <c r="F99" s="30">
         <f>IF(AND(D99=D95,E95&lt;&gt;""),E99/E95-1,"")</f>
         <v/>
       </c>
-      <c r="G99" s="16">
+      <c r="G99" s="30">
         <f>IF(C99="","",(COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C99)+(COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,C99)+1)/2)/COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6947,25 +6965,25 @@
         <f>IF(G99="","",IF(G99&lt;=20%,"Q1 Cheapest",IF(G99&lt;=40%,"Q2",IF(G99&lt;=60%,"Q3",IF(G99&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I99" s="16">
+      <c r="I99" s="30">
         <f>IFERROR(B103/B99-1,"")</f>
         <v/>
       </c>
-      <c r="J99" s="16">
+      <c r="J99" s="30">
         <f>IFERROR((B111/B99)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K99" s="16" t="n"/>
-      <c r="L99" s="16" t="n"/>
+      <c r="K99" s="30" t="n"/>
+      <c r="L99" s="30" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="18" t="n">
+      <c r="A100" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B100" s="6" t="n">
+      <c r="B100" s="24" t="n">
         <v>19638.3</v>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C100" s="25" t="n">
         <v>22.2</v>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6973,15 +6991,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E100" s="21">
+      <c r="E100" s="33">
         <f>IFERROR(B100/C100,"")</f>
         <v/>
       </c>
-      <c r="F100" s="16">
+      <c r="F100" s="30">
         <f>IF(AND(D100=D96,E96&lt;&gt;""),E100/E96-1,"")</f>
         <v/>
       </c>
-      <c r="G100" s="16">
+      <c r="G100" s="30">
         <f>IF(C100="","",(COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C100)+(COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,C100)+1)/2)/COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -6989,22 +7007,22 @@
         <f>IF(G100="","",IF(G100&lt;=20%,"Q1 Cheapest",IF(G100&lt;=40%,"Q2",IF(G100&lt;=60%,"Q3",IF(G100&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I100" s="16">
+      <c r="I100" s="30">
         <f>IFERROR(B104/B100-1,"")</f>
         <v/>
       </c>
-      <c r="J100" s="16" t="n"/>
-      <c r="K100" s="16" t="n"/>
-      <c r="L100" s="16" t="n"/>
+      <c r="J100" s="30" t="n"/>
+      <c r="K100" s="30" t="n"/>
+      <c r="L100" s="30" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="18" t="n">
+      <c r="A101" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B101" s="6" t="n">
+      <c r="B101" s="24" t="n">
         <v>21731.4</v>
       </c>
-      <c r="C101" s="7" t="n">
+      <c r="C101" s="25" t="n">
         <v>23.2</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -7012,15 +7030,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E101" s="21">
+      <c r="E101" s="33">
         <f>IFERROR(B101/C101,"")</f>
         <v/>
       </c>
-      <c r="F101" s="16">
+      <c r="F101" s="30">
         <f>IF(AND(D101=D97,E97&lt;&gt;""),E101/E97-1,"")</f>
         <v/>
       </c>
-      <c r="G101" s="16">
+      <c r="G101" s="30">
         <f>IF(C101="","",(COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C101)+(COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,C101)+1)/2)/COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7028,22 +7046,22 @@
         <f>IF(G101="","",IF(G101&lt;=20%,"Q1 Cheapest",IF(G101&lt;=40%,"Q2",IF(G101&lt;=60%,"Q3",IF(G101&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I101" s="16">
+      <c r="I101" s="30">
         <f>IFERROR(B105/B101-1,"")</f>
         <v/>
       </c>
-      <c r="J101" s="16" t="n"/>
-      <c r="K101" s="16" t="n"/>
-      <c r="L101" s="16" t="n"/>
+      <c r="J101" s="30" t="n"/>
+      <c r="K101" s="30" t="n"/>
+      <c r="L101" s="30" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="18" t="n">
+      <c r="A102" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B102" s="6" t="n">
+      <c r="B102" s="24" t="n">
         <v>22326.9</v>
       </c>
-      <c r="C102" s="7" t="n">
+      <c r="C102" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7051,15 +7069,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E102" s="21">
+      <c r="E102" s="33">
         <f>IFERROR(B102/C102,"")</f>
         <v/>
       </c>
-      <c r="F102" s="16">
+      <c r="F102" s="30">
         <f>IF(AND(D102=D98,E98&lt;&gt;""),E102/E98-1,"")</f>
         <v/>
       </c>
-      <c r="G102" s="16">
+      <c r="G102" s="30">
         <f>IF(C102="","",(COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C102)+(COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,C102)+1)/2)/COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7067,22 +7085,22 @@
         <f>IF(G102="","",IF(G102&lt;=20%,"Q1 Cheapest",IF(G102&lt;=40%,"Q2",IF(G102&lt;=60%,"Q3",IF(G102&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I102" s="16">
+      <c r="I102" s="30">
         <f>IFERROR(B106/B102-1,"")</f>
         <v/>
       </c>
-      <c r="J102" s="16" t="n"/>
-      <c r="K102" s="16" t="n"/>
-      <c r="L102" s="16" t="n"/>
+      <c r="J102" s="30" t="n"/>
+      <c r="K102" s="30" t="n"/>
+      <c r="L102" s="30" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="18" t="n">
+      <c r="A103" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B103" s="6" t="n">
+      <c r="B103" s="24" t="n">
         <v>24010.6</v>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C103" s="25" t="n">
         <v>22.9</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -7090,15 +7108,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E103" s="21">
+      <c r="E103" s="33">
         <f>IFERROR(B103/C103,"")</f>
         <v/>
       </c>
-      <c r="F103" s="16">
+      <c r="F103" s="30">
         <f>IF(AND(D103=D99,E99&lt;&gt;""),E103/E99-1,"")</f>
         <v/>
       </c>
-      <c r="G103" s="16">
+      <c r="G103" s="30">
         <f>IF(C103="","",(COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C103)+(COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,C103)+1)/2)/COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7106,22 +7124,22 @@
         <f>IF(G103="","",IF(G103&lt;=20%,"Q1 Cheapest",IF(G103&lt;=40%,"Q2",IF(G103&lt;=60%,"Q3",IF(G103&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I103" s="16">
+      <c r="I103" s="30">
         <f>IFERROR(B107/B103-1,"")</f>
         <v/>
       </c>
-      <c r="J103" s="16" t="n"/>
-      <c r="K103" s="16" t="n"/>
-      <c r="L103" s="16" t="n"/>
+      <c r="J103" s="30" t="n"/>
+      <c r="K103" s="30" t="n"/>
+      <c r="L103" s="30" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="18" t="n">
+      <c r="A104" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B104" s="6" t="n">
+      <c r="B104" s="24" t="n">
         <v>26061.3</v>
       </c>
-      <c r="C104" s="7" t="n">
+      <c r="C104" s="25" t="n">
         <v>24.3</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -7129,15 +7147,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E104" s="21">
+      <c r="E104" s="33">
         <f>IFERROR(B104/C104,"")</f>
         <v/>
       </c>
-      <c r="F104" s="16">
+      <c r="F104" s="30">
         <f>IF(AND(D104=D100,E100&lt;&gt;""),E104/E100-1,"")</f>
         <v/>
       </c>
-      <c r="G104" s="16">
+      <c r="G104" s="30">
         <f>IF(C104="","",(COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C104)+(COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,C104)+1)/2)/COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7145,22 +7163,22 @@
         <f>IF(G104="","",IF(G104&lt;=20%,"Q1 Cheapest",IF(G104&lt;=40%,"Q2",IF(G104&lt;=60%,"Q3",IF(G104&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I104" s="16">
+      <c r="I104" s="30">
         <f>IFERROR(B108/B104-1,"")</f>
         <v/>
       </c>
-      <c r="J104" s="16" t="n"/>
-      <c r="K104" s="16" t="n"/>
-      <c r="L104" s="16" t="n"/>
+      <c r="J104" s="30" t="n"/>
+      <c r="K104" s="30" t="n"/>
+      <c r="L104" s="30" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="18" t="n">
+      <c r="A105" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B105" s="6" t="n">
+      <c r="B105" s="24" t="n">
         <v>23560.6</v>
       </c>
-      <c r="C105" s="7" t="n">
+      <c r="C105" s="25" t="n">
         <v>21.8</v>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -7168,15 +7186,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E105" s="21">
+      <c r="E105" s="33">
         <f>IFERROR(B105/C105,"")</f>
         <v/>
       </c>
-      <c r="F105" s="16">
+      <c r="F105" s="30">
         <f>IF(AND(D105=D101,E101&lt;&gt;""),E105/E101-1,"")</f>
         <v/>
       </c>
-      <c r="G105" s="16">
+      <c r="G105" s="30">
         <f>IF(C105="","",(COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C105)+(COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,C105)+1)/2)/COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7184,22 +7202,22 @@
         <f>IF(G105="","",IF(G105&lt;=20%,"Q1 Cheapest",IF(G105&lt;=40%,"Q2",IF(G105&lt;=60%,"Q3",IF(G105&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I105" s="16">
+      <c r="I105" s="30">
         <f>IFERROR(B109/B105-1,"")</f>
         <v/>
       </c>
-      <c r="J105" s="16" t="n"/>
-      <c r="K105" s="16" t="n"/>
-      <c r="L105" s="16" t="n"/>
+      <c r="J105" s="30" t="n"/>
+      <c r="K105" s="30" t="n"/>
+      <c r="L105" s="30" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="18" t="n">
+      <c r="A106" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B106" s="6" t="n">
+      <c r="B106" s="24" t="n">
         <v>23519.35</v>
       </c>
-      <c r="C106" s="7" t="n">
+      <c r="C106" s="25" t="n">
         <v>21.4</v>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -7207,15 +7225,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E106" s="21">
+      <c r="E106" s="33">
         <f>IFERROR(B106/C106,"")</f>
         <v/>
       </c>
-      <c r="F106" s="16">
+      <c r="F106" s="30">
         <f>IF(AND(D106=D102,E102&lt;&gt;""),E106/E102-1,"")</f>
         <v/>
       </c>
-      <c r="G106" s="16">
+      <c r="G106" s="30">
         <f>IF(C106="","",(COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C106)+(COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,C106)+1)/2)/COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7223,22 +7241,22 @@
         <f>IF(G106="","",IF(G106&lt;=20%,"Q1 Cheapest",IF(G106&lt;=40%,"Q2",IF(G106&lt;=60%,"Q3",IF(G106&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I106" s="16">
+      <c r="I106" s="30">
         <f>IFERROR(B110/B106-1,"")</f>
         <v/>
       </c>
-      <c r="J106" s="16" t="n"/>
-      <c r="K106" s="16" t="n"/>
-      <c r="L106" s="16" t="n"/>
+      <c r="J106" s="30" t="n"/>
+      <c r="K106" s="30" t="n"/>
+      <c r="L106" s="30" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="18" t="n">
+      <c r="A107" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B107" s="6" t="n">
+      <c r="B107" s="24" t="n">
         <v>25517.05</v>
       </c>
-      <c r="C107" s="7" t="n">
+      <c r="C107" s="25" t="n">
         <v>23</v>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -7246,15 +7264,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E107" s="21">
+      <c r="E107" s="33">
         <f>IFERROR(B107/C107,"")</f>
         <v/>
       </c>
-      <c r="F107" s="16">
+      <c r="F107" s="30">
         <f>IF(AND(D107=D103,E103&lt;&gt;""),E107/E103-1,"")</f>
         <v/>
       </c>
-      <c r="G107" s="16">
+      <c r="G107" s="30">
         <f>IF(C107="","",(COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C107)+(COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,C107)+1)/2)/COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7262,22 +7280,22 @@
         <f>IF(G107="","",IF(G107&lt;=20%,"Q1 Cheapest",IF(G107&lt;=40%,"Q2",IF(G107&lt;=60%,"Q3",IF(G107&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I107" s="16">
+      <c r="I107" s="30">
         <f>IFERROR(B111/B107-1,"")</f>
         <v/>
       </c>
-      <c r="J107" s="16" t="n"/>
-      <c r="K107" s="16" t="n"/>
-      <c r="L107" s="16" t="n"/>
+      <c r="J107" s="30" t="n"/>
+      <c r="K107" s="30" t="n"/>
+      <c r="L107" s="30" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="18" t="n">
+      <c r="A108" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B108" s="6" t="n">
+      <c r="B108" s="24" t="n">
         <v>24691.95</v>
       </c>
-      <c r="C108" s="7" t="n">
+      <c r="C108" s="25" t="n">
         <v>21.8</v>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -7285,15 +7303,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E108" s="21">
+      <c r="E108" s="33">
         <f>IFERROR(B108/C108,"")</f>
         <v/>
       </c>
-      <c r="F108" s="16">
+      <c r="F108" s="30">
         <f>IF(AND(D108=D104,E104&lt;&gt;""),E108/E104-1,"")</f>
         <v/>
       </c>
-      <c r="G108" s="16">
+      <c r="G108" s="30">
         <f>IF(C108="","",(COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C108)+(COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,C108)+1)/2)/COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7301,19 +7319,19 @@
         <f>IF(G108="","",IF(G108&lt;=20%,"Q1 Cheapest",IF(G108&lt;=40%,"Q2",IF(G108&lt;=60%,"Q3",IF(G108&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I108" s="16" t="n"/>
-      <c r="J108" s="16" t="n"/>
-      <c r="K108" s="16" t="n"/>
-      <c r="L108" s="16" t="n"/>
+      <c r="I108" s="30" t="n"/>
+      <c r="J108" s="30" t="n"/>
+      <c r="K108" s="30" t="n"/>
+      <c r="L108" s="30" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="18" t="n">
+      <c r="A109" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B109" s="6" t="n">
+      <c r="B109" s="24" t="n">
         <v>25971.05</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C109" s="25" t="n">
         <v>22.8</v>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -7321,15 +7339,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E109" s="21">
+      <c r="E109" s="33">
         <f>IFERROR(B109/C109,"")</f>
         <v/>
       </c>
-      <c r="F109" s="16">
+      <c r="F109" s="30">
         <f>IF(AND(D109=D105,E105&lt;&gt;""),E109/E105-1,"")</f>
         <v/>
       </c>
-      <c r="G109" s="16">
+      <c r="G109" s="30">
         <f>IF(C109="","",(COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C109)+(COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,C109)+1)/2)/COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7337,19 +7355,19 @@
         <f>IF(G109="","",IF(G109&lt;=20%,"Q1 Cheapest",IF(G109&lt;=40%,"Q2",IF(G109&lt;=60%,"Q3",IF(G109&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I109" s="16" t="n"/>
-      <c r="J109" s="16" t="n"/>
-      <c r="K109" s="16" t="n"/>
-      <c r="L109" s="16" t="n"/>
+      <c r="I109" s="30" t="n"/>
+      <c r="J109" s="30" t="n"/>
+      <c r="K109" s="30" t="n"/>
+      <c r="L109" s="30" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="18" t="n">
+      <c r="A110" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B110" s="6" t="n">
+      <c r="B110" s="24" t="n">
         <v>22549.65</v>
       </c>
-      <c r="C110" s="7" t="n">
+      <c r="C110" s="25" t="n">
         <v>19.6</v>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -7357,15 +7375,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E110" s="21">
+      <c r="E110" s="33">
         <f>IFERROR(B110/C110,"")</f>
         <v/>
       </c>
-      <c r="F110" s="16">
+      <c r="F110" s="30">
         <f>IF(AND(D110=D106,E106&lt;&gt;""),E110/E106-1,"")</f>
         <v/>
       </c>
-      <c r="G110" s="16">
+      <c r="G110" s="30">
         <f>IF(C110="","",(COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C110)+(COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,C110)+1)/2)/COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7373,19 +7391,19 @@
         <f>IF(G110="","",IF(G110&lt;=20%,"Q1 Cheapest",IF(G110&lt;=40%,"Q2",IF(G110&lt;=60%,"Q3",IF(G110&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I110" s="16" t="n"/>
-      <c r="J110" s="16" t="n"/>
-      <c r="K110" s="16" t="n"/>
-      <c r="L110" s="16" t="n"/>
+      <c r="I110" s="30" t="n"/>
+      <c r="J110" s="30" t="n"/>
+      <c r="K110" s="30" t="n"/>
+      <c r="L110" s="30" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="18" t="n">
+      <c r="A111" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B111" s="6" t="n">
+      <c r="B111" s="24" t="n">
         <v>23865.75</v>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C111" s="25" t="n">
         <v>20.6</v>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -7393,15 +7411,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E111" s="21">
+      <c r="E111" s="33">
         <f>IFERROR(B111/C111,"")</f>
         <v/>
       </c>
-      <c r="F111" s="16">
+      <c r="F111" s="30">
         <f>IF(AND(D111=D107,E107&lt;&gt;""),E111/E107-1,"")</f>
         <v/>
       </c>
-      <c r="G111" s="16">
+      <c r="G111" s="30">
         <f>IF(C111="","",(COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C111)+(COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,C111)+1)/2)/COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,"&gt;0"))</f>
         <v/>
       </c>
@@ -7409,10 +7427,10 @@
         <f>IF(G111="","",IF(G111&lt;=20%,"Q1 Cheapest",IF(G111&lt;=40%,"Q2",IF(G111&lt;=60%,"Q3",IF(G111&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I111" s="16" t="n"/>
-      <c r="J111" s="16" t="n"/>
-      <c r="K111" s="16" t="n"/>
-      <c r="L111" s="16" t="n"/>
+      <c r="I111" s="30" t="n"/>
+      <c r="J111" s="30" t="n"/>
+      <c r="K111" s="30" t="n"/>
+      <c r="L111" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -7489,30 +7507,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>23346.4</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>19.74</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.0387820820751</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -7522,30 +7540,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>23414.3</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>19.79</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0393954034603</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -7555,30 +7573,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>23329</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>19.72</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.0530303030303</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.0392637770816</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -7594,6 +7612,1258 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="n">
+        <v>0.9998999999999999</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Indices Market Capitalisation &amp; Weightage</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>0.09849999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ICICI Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>0.09449999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.07829999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>0.0398</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="n">
+        <v>0.0361</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>0.0339</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kotak Mahindra Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="n">
+        <v>0.0266</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bajaj Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="n">
+        <v>0.0257</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ITC Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>0.0224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="n">
+        <v>0.0222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Eternal Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="n">
+        <v>0.0215</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E20" s="37" t="n">
+        <v>0.0191</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="E21" s="37" t="n">
+        <v>0.0191</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maruti Suzuki India Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E23" s="37" t="n">
+        <v>0.0158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NTPC Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>0.0141</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Shriram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>0.0141</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tata Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E26" s="37" t="n">
+        <v>0.0138</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bharat Electronics Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>0.0135</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="n">
+        <v>0.0133</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n">
+        <v>0.0126</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UltraTech Cement Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="n">
+        <v>0.0123</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bajaj Auto Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="n">
+        <v>0.0122</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Grasim Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Construction Materials</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="n">
+        <v>0.0115</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JSW Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="n">
+        <v>0.0111</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Asian Paints Ltd.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>InterGlobe Aviation Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="n">
+        <v>0.0108</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="n">
+        <v>0.0108</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="n">
+        <v>0.0107</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Bajaj Finserv Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="n">
+        <v>0.0106</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nestle India Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="n">
+        <v>0.0097</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Coal India Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Trent Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="n">
+        <v>0.0083</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="n">
+        <v>0.008199999999999999</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Adani Enterprises Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="E46" s="37" t="n">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cipla Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="n">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Jio Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E48" s="37" t="n">
+        <v>0.0072</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SBI Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E49" s="37" t="n">
+        <v>0.0071</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Max Healthcare Institute Ltd.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="E51" s="37" t="n">
+        <v>0.0064</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Tata Consumer Products Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="E52" s="37" t="n">
+        <v>0.0061</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="E53" s="37" t="n">
+        <v>0.0059</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HDFC Life Insurance Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="E54" s="37" t="n">
+        <v>0.0053</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wipro Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E55" s="37" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23329</v>
+        <v>23446.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.72</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1183.012170385396</v>
+        <v>1182.986881937437</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.039263777081608</v>
+        <v>0.03918790439368003</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05070993914807303</v>
+        <v>0.05045408678102926</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.7055108326432</v>
+        <v>35.67516175747201</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.99953203767174</v>
+        <v>76.99042731512039</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.57304957086787</v>
+        <v>20.57195050078845</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24338.16802427873</v>
+        <v>24336.34757829902</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04325809182899931</v>
+        <v>0.03793897582181893</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29840458194314</v>
+        <v>22.29747459956825</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26379.2840006162</v>
+        <v>26377.61995162244</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1307507394494494</v>
+        <v>0.1249987184444123</v>
       </c>
     </row>
     <row r="16">
@@ -7445,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7602,6 +7602,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>23446.8</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.0530303030303</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0391879043937</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23446.8</v>
+        <v>23063.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.82</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05303030303030303</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1182.986881937437</v>
+        <v>1182.723076923077</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03918790439368003</v>
+        <v>0.03890484948564765</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05045408678102926</v>
+        <v>0.05128205128205128</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.6969696969697</v>
+        <v>98.48484848484848</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.67516175747201</v>
+        <v>35.56193979425906</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.99042731512039</v>
+        <v>79.60797587767166</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.57195050078845</v>
+        <v>20.56785024826352</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24336.34757829902</v>
+        <v>24326.0711313193</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03793897582181893</v>
+        <v>0.05476155119300108</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29747459956825</v>
+        <v>22.29400515512408</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26377.61995162244</v>
+        <v>26367.63437400729</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1249987184444123</v>
+        <v>0.1432823156473888</v>
       </c>
     </row>
     <row r="16">
@@ -7445,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7635,6 +7635,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>23063.1</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.0151515151515</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.0389048494856</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23063.1</v>
+        <v>23140.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.5</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.02272727272727273</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1182.723076923077</v>
+        <v>1183.052147239264</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03890484948564765</v>
+        <v>0.03899705870431536</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.05112474437627812</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>98.48484848484848</v>
+        <v>97.72727272727273</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.56193979425906</v>
+        <v>35.59882348172614</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.60797587767166</v>
+        <v>79.08873795360876</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.56785024826352</v>
+        <v>20.56918596465965</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24326.0711313193</v>
+        <v>24334.41962245433</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05476155119300108</v>
+        <v>0.05159437447135251</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29400515512408</v>
+        <v>22.29513537669003</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26367.63437400729</v>
+        <v>26376.30778038322</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1432823156473888</v>
+        <v>0.1398330969677932</v>
       </c>
     </row>
     <row r="16">
@@ -7445,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7668,6 +7668,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>23140.5</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0389970587043</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23140.5</v>
+        <v>22780.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.56</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1183.052147239264</v>
+        <v>1182.77518172378</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03899705870431536</v>
+        <v>0.03910858522460492</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05112474437627812</v>
+        <v>0.05192107995846313</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.72727272727273</v>
+        <v>99.24242424242425</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.59882348172614</v>
+        <v>35.64343408984197</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.08873795360876</v>
+        <v>80.16272719664956</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.56918596465965</v>
+        <v>20.57080150596784</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24334.41962245433</v>
+        <v>24330.63348942492</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05159437447135251</v>
+        <v>0.06805822980103016</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29513537669003</v>
+        <v>22.29650237318159</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26376.30778038322</v>
+        <v>26371.74964624453</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1398330969677932</v>
+        <v>0.157658482512024</v>
       </c>
     </row>
     <row r="16">
@@ -7445,13 +7445,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -7701,6 +7701,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>22780.25</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.00757575757576</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.0391085852246</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22780.25</v>
+        <v>22716.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.26</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1182.77518172378</v>
+        <v>1183.135416666667</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03910858522460492</v>
+        <v>0.03929995318295054</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05192107995846313</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.64343408984197</v>
+        <v>35.71998127318022</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.16272719664956</v>
+        <v>80.18569135165103</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.57080150596784</v>
+        <v>20.57357360753588</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24330.63348942492</v>
+        <v>24341.3235824743</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06805822980103016</v>
+        <v>0.07154029205916057</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29650237318159</v>
+        <v>22.29884799758531</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26371.74964624453</v>
+        <v>26382.55681680976</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.157658482512024</v>
+        <v>0.1613983332075679</v>
       </c>
     </row>
     <row r="16">
@@ -7445,7 +7445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7734,6 +7734,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>22716.2</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.00757575757576</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.039299953183</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,8 +569,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22716.2</v>
+        <v>22620.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.2</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007575757575757576</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1183.135416666667</v>
+        <v>1168.411673553719</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03929995318295054</v>
+        <v>0.03305573568548059</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.05165289256198347</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.24242424242425</v>
+        <v>98.50746268656717</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.71998127318022</v>
+        <v>33.22229427419224</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.18569135165103</v>
+        <v>78.92191216285468</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.57357360753588</v>
+        <v>20.44397163237557</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24341.3235824743</v>
+        <v>23886.9751090687</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07154029205916057</v>
+        <v>0.05599027026733316</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29884799758531</v>
+        <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26382.55681680976</v>
+        <v>25950.4232696281</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1613983332075679</v>
+        <v>0.147210743801653</v>
       </c>
     </row>
     <row r="16">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.3794110863381257</v>
+        <v>0.379411086338</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.2804292628723728</v>
+        <v>0.280429262872</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.2330247834427452</v>
+        <v>0.233024783443</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>0.1639263551809637</v>
+        <v>0.163926355181</v>
       </c>
       <c r="G18" s="30" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>24</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.1900379979058278</v>
+        <v>0.179797624285</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1208474326591867</v>
+        <v>0.120847432659</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.1216016486559849</v>
+        <v>0.121601648656</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>0.1224198770703966</v>
+        <v>0.1224198770705</v>
       </c>
       <c r="G19" s="30" t="n">
         <v>0.05</v>
@@ -866,19 +866,19 @@
         <v>20</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.1068255572697771</v>
+        <v>0.10682555727</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.0939521989345575</v>
+        <v>0.0833084895083</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.1126009545572526</v>
+        <v>0.112600954557</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>0.1144515211675757</v>
+        <v>0.1144515211675</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="21">
@@ -891,16 +891,16 @@
         <v>23</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.0627410393742764</v>
+        <v>0.06274103937430001</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>0.060027361417227</v>
+        <v>0.0600273614172</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.08987020932283746</v>
+        <v>0.08987020932285</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>0.1072524436331572</v>
+        <v>0.104325192957</v>
       </c>
       <c r="G21" s="30" t="n">
         <v>0.2105263157894737</v>
@@ -916,16 +916,16 @@
         <v>23</v>
       </c>
       <c r="C22" s="30" t="n">
-        <v>0.0432896067488568</v>
+        <v>0.0432896067489</v>
       </c>
       <c r="D22" s="30" t="n">
-        <v>0.1378754251395846</v>
+        <v>0.13787542514</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1207882016172213</v>
+        <v>0.117960352541</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>0.07509863754171059</v>
+        <v>0.07509863754169999</v>
       </c>
       <c r="G22" s="30" t="n">
         <v>0.1363636363636364</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
@@ -978,7 +978,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2297,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2313,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2325,7 +2344,7 @@
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="33" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
@@ -2413,7 +2432,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,C2)+1)/2)/COUNTIFS($D$2:$D$111,D2,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$112,D2,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$112,D2,$C$2:$C$112,C2)+1)/2)/COUNTIFS($D$2:$D$112,D2,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2458,7 +2477,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,C3)+1)/2)/COUNTIFS($D$2:$D$111,D3,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$112,D3,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$112,D3,$C$2:$C$112,C3)+1)/2)/COUNTIFS($D$2:$D$112,D3,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2503,7 +2522,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,C4)+1)/2)/COUNTIFS($D$2:$D$111,D4,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$112,D4,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$112,D4,$C$2:$C$112,C4)+1)/2)/COUNTIFS($D$2:$D$112,D4,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2548,7 +2567,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,C5)+1)/2)/COUNTIFS($D$2:$D$111,D5,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$112,D5,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$112,D5,$C$2:$C$112,C5)+1)/2)/COUNTIFS($D$2:$D$112,D5,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2596,7 +2615,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,C6)+1)/2)/COUNTIFS($D$2:$D$111,D6,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$112,D6,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$112,D6,$C$2:$C$112,C6)+1)/2)/COUNTIFS($D$2:$D$112,D6,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2644,7 +2663,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,C7)+1)/2)/COUNTIFS($D$2:$D$111,D7,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$112,D7,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$112,D7,$C$2:$C$112,C7)+1)/2)/COUNTIFS($D$2:$D$112,D7,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2692,7 +2711,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,C8)+1)/2)/COUNTIFS($D$2:$D$111,D8,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$112,D8,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$112,D8,$C$2:$C$112,C8)+1)/2)/COUNTIFS($D$2:$D$112,D8,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2740,7 +2759,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,C9)+1)/2)/COUNTIFS($D$2:$D$111,D9,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$112,D9,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$112,D9,$C$2:$C$112,C9)+1)/2)/COUNTIFS($D$2:$D$112,D9,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2788,7 +2807,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,C10)+1)/2)/COUNTIFS($D$2:$D$111,D10,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$112,D10,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$112,D10,$C$2:$C$112,C10)+1)/2)/COUNTIFS($D$2:$D$112,D10,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2836,7 +2855,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,C11)+1)/2)/COUNTIFS($D$2:$D$111,D11,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$112,D11,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$112,D11,$C$2:$C$112,C11)+1)/2)/COUNTIFS($D$2:$D$112,D11,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2884,7 +2903,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,C12)+1)/2)/COUNTIFS($D$2:$D$111,D12,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$112,D12,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$112,D12,$C$2:$C$112,C12)+1)/2)/COUNTIFS($D$2:$D$112,D12,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2932,7 +2951,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,C13)+1)/2)/COUNTIFS($D$2:$D$111,D13,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$112,D13,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$112,D13,$C$2:$C$112,C13)+1)/2)/COUNTIFS($D$2:$D$112,D13,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2980,7 +2999,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,C14)+1)/2)/COUNTIFS($D$2:$D$111,D14,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$112,D14,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$112,D14,$C$2:$C$112,C14)+1)/2)/COUNTIFS($D$2:$D$112,D14,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -3028,7 +3047,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,C15)+1)/2)/COUNTIFS($D$2:$D$111,D15,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$112,D15,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$112,D15,$C$2:$C$112,C15)+1)/2)/COUNTIFS($D$2:$D$112,D15,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3076,7 +3095,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,C16)+1)/2)/COUNTIFS($D$2:$D$111,D16,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$112,D16,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$112,D16,$C$2:$C$112,C16)+1)/2)/COUNTIFS($D$2:$D$112,D16,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3124,7 +3143,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,C17)+1)/2)/COUNTIFS($D$2:$D$111,D17,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$112,D17,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$112,D17,$C$2:$C$112,C17)+1)/2)/COUNTIFS($D$2:$D$112,D17,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3172,7 +3191,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,C18)+1)/2)/COUNTIFS($D$2:$D$111,D18,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$112,D18,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$112,D18,$C$2:$C$112,C18)+1)/2)/COUNTIFS($D$2:$D$112,D18,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3220,7 +3239,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,C19)+1)/2)/COUNTIFS($D$2:$D$111,D19,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$112,D19,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$112,D19,$C$2:$C$112,C19)+1)/2)/COUNTIFS($D$2:$D$112,D19,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3268,7 +3287,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,C20)+1)/2)/COUNTIFS($D$2:$D$111,D20,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$112,D20,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$112,D20,$C$2:$C$112,C20)+1)/2)/COUNTIFS($D$2:$D$112,D20,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3316,7 +3335,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,C21)+1)/2)/COUNTIFS($D$2:$D$111,D21,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$112,D21,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$112,D21,$C$2:$C$112,C21)+1)/2)/COUNTIFS($D$2:$D$112,D21,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3364,7 +3383,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,C22)+1)/2)/COUNTIFS($D$2:$D$111,D22,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$112,D22,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$112,D22,$C$2:$C$112,C22)+1)/2)/COUNTIFS($D$2:$D$112,D22,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3412,7 +3431,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,C23)+1)/2)/COUNTIFS($D$2:$D$111,D23,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$112,D23,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$112,D23,$C$2:$C$112,C23)+1)/2)/COUNTIFS($D$2:$D$112,D23,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3460,7 +3479,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,C24)+1)/2)/COUNTIFS($D$2:$D$111,D24,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$112,D24,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$112,D24,$C$2:$C$112,C24)+1)/2)/COUNTIFS($D$2:$D$112,D24,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3508,7 +3527,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,C25)+1)/2)/COUNTIFS($D$2:$D$111,D25,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$112,D25,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$112,D25,$C$2:$C$112,C25)+1)/2)/COUNTIFS($D$2:$D$112,D25,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3556,7 +3575,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,C26)+1)/2)/COUNTIFS($D$2:$D$111,D26,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$112,D26,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$112,D26,$C$2:$C$112,C26)+1)/2)/COUNTIFS($D$2:$D$112,D26,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3604,7 +3623,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,C27)+1)/2)/COUNTIFS($D$2:$D$111,D27,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$112,D27,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$112,D27,$C$2:$C$112,C27)+1)/2)/COUNTIFS($D$2:$D$112,D27,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3652,7 +3671,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,C28)+1)/2)/COUNTIFS($D$2:$D$111,D28,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$112,D28,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$112,D28,$C$2:$C$112,C28)+1)/2)/COUNTIFS($D$2:$D$112,D28,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3700,7 +3719,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,C29)+1)/2)/COUNTIFS($D$2:$D$111,D29,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$112,D29,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$112,D29,$C$2:$C$112,C29)+1)/2)/COUNTIFS($D$2:$D$112,D29,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3748,7 +3767,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,C30)+1)/2)/COUNTIFS($D$2:$D$111,D30,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$112,D30,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$112,D30,$C$2:$C$112,C30)+1)/2)/COUNTIFS($D$2:$D$112,D30,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3796,7 +3815,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,C31)+1)/2)/COUNTIFS($D$2:$D$111,D31,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$112,D31,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$112,D31,$C$2:$C$112,C31)+1)/2)/COUNTIFS($D$2:$D$112,D31,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3844,7 +3863,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,C32)+1)/2)/COUNTIFS($D$2:$D$111,D32,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$112,D32,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$112,D32,$C$2:$C$112,C32)+1)/2)/COUNTIFS($D$2:$D$112,D32,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3892,7 +3911,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,C33)+1)/2)/COUNTIFS($D$2:$D$111,D33,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$112,D33,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$112,D33,$C$2:$C$112,C33)+1)/2)/COUNTIFS($D$2:$D$112,D33,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3940,7 +3959,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,C34)+1)/2)/COUNTIFS($D$2:$D$111,D34,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$112,D34,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$112,D34,$C$2:$C$112,C34)+1)/2)/COUNTIFS($D$2:$D$112,D34,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3988,7 +4007,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,C35)+1)/2)/COUNTIFS($D$2:$D$111,D35,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$112,D35,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$112,D35,$C$2:$C$112,C35)+1)/2)/COUNTIFS($D$2:$D$112,D35,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -4036,7 +4055,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,C36)+1)/2)/COUNTIFS($D$2:$D$111,D36,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$112,D36,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$112,D36,$C$2:$C$112,C36)+1)/2)/COUNTIFS($D$2:$D$112,D36,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -4084,7 +4103,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,C37)+1)/2)/COUNTIFS($D$2:$D$111,D37,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$112,D37,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$112,D37,$C$2:$C$112,C37)+1)/2)/COUNTIFS($D$2:$D$112,D37,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -4132,7 +4151,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,C38)+1)/2)/COUNTIFS($D$2:$D$111,D38,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$112,D38,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$112,D38,$C$2:$C$112,C38)+1)/2)/COUNTIFS($D$2:$D$112,D38,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4180,7 +4199,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,C39)+1)/2)/COUNTIFS($D$2:$D$111,D39,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$112,D39,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$112,D39,$C$2:$C$112,C39)+1)/2)/COUNTIFS($D$2:$D$112,D39,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4228,7 +4247,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,C40)+1)/2)/COUNTIFS($D$2:$D$111,D40,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$112,D40,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$112,D40,$C$2:$C$112,C40)+1)/2)/COUNTIFS($D$2:$D$112,D40,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4276,7 +4295,7 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,C41)+1)/2)/COUNTIFS($D$2:$D$111,D41,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$112,D41,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$112,D41,$C$2:$C$112,C41)+1)/2)/COUNTIFS($D$2:$D$112,D41,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
@@ -4324,7 +4343,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,C42)+1)/2)/COUNTIFS($D$2:$D$111,D42,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$112,D42,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$112,D42,$C$2:$C$112,C42)+1)/2)/COUNTIFS($D$2:$D$112,D42,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4372,7 +4391,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,C43)+1)/2)/COUNTIFS($D$2:$D$111,D43,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$112,D43,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$112,D43,$C$2:$C$112,C43)+1)/2)/COUNTIFS($D$2:$D$112,D43,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4420,7 +4439,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,C44)+1)/2)/COUNTIFS($D$2:$D$111,D44,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$112,D44,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$112,D44,$C$2:$C$112,C44)+1)/2)/COUNTIFS($D$2:$D$112,D44,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4468,7 +4487,7 @@
         <v/>
       </c>
       <c r="G45" s="30">
-        <f>IF(C45="","",(COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,C45)+1)/2)/COUNTIFS($D$2:$D$111,D45,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$112,D45,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$112,D45,$C$2:$C$112,C45)+1)/2)/COUNTIFS($D$2:$D$112,D45,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H45">
@@ -4516,7 +4535,7 @@
         <v/>
       </c>
       <c r="G46" s="30">
-        <f>IF(C46="","",(COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,C46)+1)/2)/COUNTIFS($D$2:$D$111,D46,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C46="","",(COUNTIFS($D$2:$D$112,D46,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C46)+(COUNTIFS($D$2:$D$112,D46,$C$2:$C$112,C46)+1)/2)/COUNTIFS($D$2:$D$112,D46,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H46">
@@ -4564,7 +4583,7 @@
         <v/>
       </c>
       <c r="G47" s="30">
-        <f>IF(C47="","",(COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,C47)+1)/2)/COUNTIFS($D$2:$D$111,D47,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C47="","",(COUNTIFS($D$2:$D$112,D47,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C47)+(COUNTIFS($D$2:$D$112,D47,$C$2:$C$112,C47)+1)/2)/COUNTIFS($D$2:$D$112,D47,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H47">
@@ -4612,7 +4631,7 @@
         <v/>
       </c>
       <c r="G48" s="30">
-        <f>IF(C48="","",(COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,C48)+1)/2)/COUNTIFS($D$2:$D$111,D48,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C48="","",(COUNTIFS($D$2:$D$112,D48,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C48)+(COUNTIFS($D$2:$D$112,D48,$C$2:$C$112,C48)+1)/2)/COUNTIFS($D$2:$D$112,D48,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H48">
@@ -4660,7 +4679,7 @@
         <v/>
       </c>
       <c r="G49" s="30">
-        <f>IF(C49="","",(COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,C49)+1)/2)/COUNTIFS($D$2:$D$111,D49,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C49="","",(COUNTIFS($D$2:$D$112,D49,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C49)+(COUNTIFS($D$2:$D$112,D49,$C$2:$C$112,C49)+1)/2)/COUNTIFS($D$2:$D$112,D49,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H49">
@@ -4708,7 +4727,7 @@
         <v/>
       </c>
       <c r="G50" s="30">
-        <f>IF(C50="","",(COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,C50)+1)/2)/COUNTIFS($D$2:$D$111,D50,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C50="","",(COUNTIFS($D$2:$D$112,D50,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C50)+(COUNTIFS($D$2:$D$112,D50,$C$2:$C$112,C50)+1)/2)/COUNTIFS($D$2:$D$112,D50,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H50">
@@ -4756,7 +4775,7 @@
         <v/>
       </c>
       <c r="G51" s="30">
-        <f>IF(C51="","",(COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,C51)+1)/2)/COUNTIFS($D$2:$D$111,D51,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C51="","",(COUNTIFS($D$2:$D$112,D51,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C51)+(COUNTIFS($D$2:$D$112,D51,$C$2:$C$112,C51)+1)/2)/COUNTIFS($D$2:$D$112,D51,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H51">
@@ -4804,7 +4823,7 @@
         <v/>
       </c>
       <c r="G52" s="30">
-        <f>IF(C52="","",(COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,C52)+1)/2)/COUNTIFS($D$2:$D$111,D52,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C52="","",(COUNTIFS($D$2:$D$112,D52,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C52)+(COUNTIFS($D$2:$D$112,D52,$C$2:$C$112,C52)+1)/2)/COUNTIFS($D$2:$D$112,D52,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H52">
@@ -4852,7 +4871,7 @@
         <v/>
       </c>
       <c r="G53" s="30">
-        <f>IF(C53="","",(COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,C53)+1)/2)/COUNTIFS($D$2:$D$111,D53,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C53="","",(COUNTIFS($D$2:$D$112,D53,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C53)+(COUNTIFS($D$2:$D$112,D53,$C$2:$C$112,C53)+1)/2)/COUNTIFS($D$2:$D$112,D53,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H53">
@@ -4900,7 +4919,7 @@
         <v/>
       </c>
       <c r="G54" s="30">
-        <f>IF(C54="","",(COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,C54)+1)/2)/COUNTIFS($D$2:$D$111,D54,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C54="","",(COUNTIFS($D$2:$D$112,D54,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C54)+(COUNTIFS($D$2:$D$112,D54,$C$2:$C$112,C54)+1)/2)/COUNTIFS($D$2:$D$112,D54,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H54">
@@ -4948,7 +4967,7 @@
         <v/>
       </c>
       <c r="G55" s="30">
-        <f>IF(C55="","",(COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,C55)+1)/2)/COUNTIFS($D$2:$D$111,D55,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C55="","",(COUNTIFS($D$2:$D$112,D55,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C55)+(COUNTIFS($D$2:$D$112,D55,$C$2:$C$112,C55)+1)/2)/COUNTIFS($D$2:$D$112,D55,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H55">
@@ -4996,7 +5015,7 @@
         <v/>
       </c>
       <c r="G56" s="30">
-        <f>IF(C56="","",(COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,C56)+1)/2)/COUNTIFS($D$2:$D$111,D56,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C56="","",(COUNTIFS($D$2:$D$112,D56,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C56)+(COUNTIFS($D$2:$D$112,D56,$C$2:$C$112,C56)+1)/2)/COUNTIFS($D$2:$D$112,D56,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H56">
@@ -5044,7 +5063,7 @@
         <v/>
       </c>
       <c r="G57" s="30">
-        <f>IF(C57="","",(COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,C57)+1)/2)/COUNTIFS($D$2:$D$111,D57,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C57="","",(COUNTIFS($D$2:$D$112,D57,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C57)+(COUNTIFS($D$2:$D$112,D57,$C$2:$C$112,C57)+1)/2)/COUNTIFS($D$2:$D$112,D57,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H57">
@@ -5092,7 +5111,7 @@
         <v/>
       </c>
       <c r="G58" s="30">
-        <f>IF(C58="","",(COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,C58)+1)/2)/COUNTIFS($D$2:$D$111,D58,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C58="","",(COUNTIFS($D$2:$D$112,D58,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C58)+(COUNTIFS($D$2:$D$112,D58,$C$2:$C$112,C58)+1)/2)/COUNTIFS($D$2:$D$112,D58,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H58">
@@ -5140,7 +5159,7 @@
         <v/>
       </c>
       <c r="G59" s="30">
-        <f>IF(C59="","",(COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,C59)+1)/2)/COUNTIFS($D$2:$D$111,D59,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C59="","",(COUNTIFS($D$2:$D$112,D59,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C59)+(COUNTIFS($D$2:$D$112,D59,$C$2:$C$112,C59)+1)/2)/COUNTIFS($D$2:$D$112,D59,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H59">
@@ -5188,7 +5207,7 @@
         <v/>
       </c>
       <c r="G60" s="30">
-        <f>IF(C60="","",(COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C60)+(COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,C60)+1)/2)/COUNTIFS($D$2:$D$111,D60,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C60="","",(COUNTIFS($D$2:$D$112,D60,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C60)+(COUNTIFS($D$2:$D$112,D60,$C$2:$C$112,C60)+1)/2)/COUNTIFS($D$2:$D$112,D60,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H60">
@@ -5236,7 +5255,7 @@
         <v/>
       </c>
       <c r="G61" s="30">
-        <f>IF(C61="","",(COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C61)+(COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,C61)+1)/2)/COUNTIFS($D$2:$D$111,D61,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C61="","",(COUNTIFS($D$2:$D$112,D61,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C61)+(COUNTIFS($D$2:$D$112,D61,$C$2:$C$112,C61)+1)/2)/COUNTIFS($D$2:$D$112,D61,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H61">
@@ -5284,7 +5303,7 @@
         <v/>
       </c>
       <c r="G62" s="30">
-        <f>IF(C62="","",(COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C62)+(COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,C62)+1)/2)/COUNTIFS($D$2:$D$111,D62,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C62="","",(COUNTIFS($D$2:$D$112,D62,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C62)+(COUNTIFS($D$2:$D$112,D62,$C$2:$C$112,C62)+1)/2)/COUNTIFS($D$2:$D$112,D62,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H62">
@@ -5332,7 +5351,7 @@
         <v/>
       </c>
       <c r="G63" s="30">
-        <f>IF(C63="","",(COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C63)+(COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,C63)+1)/2)/COUNTIFS($D$2:$D$111,D63,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C63="","",(COUNTIFS($D$2:$D$112,D63,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C63)+(COUNTIFS($D$2:$D$112,D63,$C$2:$C$112,C63)+1)/2)/COUNTIFS($D$2:$D$112,D63,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H63">
@@ -5380,7 +5399,7 @@
         <v/>
       </c>
       <c r="G64" s="30">
-        <f>IF(C64="","",(COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C64)+(COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,C64)+1)/2)/COUNTIFS($D$2:$D$111,D64,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C64="","",(COUNTIFS($D$2:$D$112,D64,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C64)+(COUNTIFS($D$2:$D$112,D64,$C$2:$C$112,C64)+1)/2)/COUNTIFS($D$2:$D$112,D64,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H64">
@@ -5428,7 +5447,7 @@
         <v/>
       </c>
       <c r="G65" s="30">
-        <f>IF(C65="","",(COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C65)+(COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,C65)+1)/2)/COUNTIFS($D$2:$D$111,D65,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C65="","",(COUNTIFS($D$2:$D$112,D65,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C65)+(COUNTIFS($D$2:$D$112,D65,$C$2:$C$112,C65)+1)/2)/COUNTIFS($D$2:$D$112,D65,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H65">
@@ -5476,7 +5495,7 @@
         <v/>
       </c>
       <c r="G66" s="30">
-        <f>IF(C66="","",(COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C66)+(COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,C66)+1)/2)/COUNTIFS($D$2:$D$111,D66,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C66="","",(COUNTIFS($D$2:$D$112,D66,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C66)+(COUNTIFS($D$2:$D$112,D66,$C$2:$C$112,C66)+1)/2)/COUNTIFS($D$2:$D$112,D66,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H66">
@@ -5524,7 +5543,7 @@
         <v/>
       </c>
       <c r="G67" s="30">
-        <f>IF(C67="","",(COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C67)+(COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,C67)+1)/2)/COUNTIFS($D$2:$D$111,D67,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C67="","",(COUNTIFS($D$2:$D$112,D67,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C67)+(COUNTIFS($D$2:$D$112,D67,$C$2:$C$112,C67)+1)/2)/COUNTIFS($D$2:$D$112,D67,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H67">
@@ -5572,7 +5591,7 @@
         <v/>
       </c>
       <c r="G68" s="30">
-        <f>IF(C68="","",(COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C68)+(COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,C68)+1)/2)/COUNTIFS($D$2:$D$111,D68,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C68="","",(COUNTIFS($D$2:$D$112,D68,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C68)+(COUNTIFS($D$2:$D$112,D68,$C$2:$C$112,C68)+1)/2)/COUNTIFS($D$2:$D$112,D68,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H68">
@@ -5620,7 +5639,7 @@
         <v/>
       </c>
       <c r="G69" s="30">
-        <f>IF(C69="","",(COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C69)+(COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,C69)+1)/2)/COUNTIFS($D$2:$D$111,D69,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C69="","",(COUNTIFS($D$2:$D$112,D69,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C69)+(COUNTIFS($D$2:$D$112,D69,$C$2:$C$112,C69)+1)/2)/COUNTIFS($D$2:$D$112,D69,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H69">
@@ -5668,7 +5687,7 @@
         <v/>
       </c>
       <c r="G70" s="30">
-        <f>IF(C70="","",(COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C70)+(COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,C70)+1)/2)/COUNTIFS($D$2:$D$111,D70,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C70="","",(COUNTIFS($D$2:$D$112,D70,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C70)+(COUNTIFS($D$2:$D$112,D70,$C$2:$C$112,C70)+1)/2)/COUNTIFS($D$2:$D$112,D70,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H70">
@@ -5716,7 +5735,7 @@
         <v/>
       </c>
       <c r="G71" s="30">
-        <f>IF(C71="","",(COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C71)+(COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,C71)+1)/2)/COUNTIFS($D$2:$D$111,D71,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C71="","",(COUNTIFS($D$2:$D$112,D71,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C71)+(COUNTIFS($D$2:$D$112,D71,$C$2:$C$112,C71)+1)/2)/COUNTIFS($D$2:$D$112,D71,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H71">
@@ -5764,7 +5783,7 @@
         <v/>
       </c>
       <c r="G72" s="30">
-        <f>IF(C72="","",(COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C72)+(COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,C72)+1)/2)/COUNTIFS($D$2:$D$111,D72,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C72="","",(COUNTIFS($D$2:$D$112,D72,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C72)+(COUNTIFS($D$2:$D$112,D72,$C$2:$C$112,C72)+1)/2)/COUNTIFS($D$2:$D$112,D72,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H72">
@@ -5783,7 +5802,10 @@
         <f>IFERROR((B92/B72)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L72" s="30" t="n"/>
+      <c r="L72" s="30">
+        <f>IFERROR((B112/B72)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="n">
@@ -5809,7 +5831,7 @@
         <v/>
       </c>
       <c r="G73" s="30">
-        <f>IF(C73="","",(COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C73)+(COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,C73)+1)/2)/COUNTIFS($D$2:$D$111,D73,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C73="","",(COUNTIFS($D$2:$D$112,D73,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C73)+(COUNTIFS($D$2:$D$112,D73,$C$2:$C$112,C73)+1)/2)/COUNTIFS($D$2:$D$112,D73,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H73">
@@ -5854,7 +5876,7 @@
         <v/>
       </c>
       <c r="G74" s="30">
-        <f>IF(C74="","",(COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C74)+(COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,C74)+1)/2)/COUNTIFS($D$2:$D$111,D74,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C74="","",(COUNTIFS($D$2:$D$112,D74,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C74)+(COUNTIFS($D$2:$D$112,D74,$C$2:$C$112,C74)+1)/2)/COUNTIFS($D$2:$D$112,D74,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H74">
@@ -5899,7 +5921,7 @@
         <v/>
       </c>
       <c r="G75" s="30">
-        <f>IF(C75="","",(COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C75)+(COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,C75)+1)/2)/COUNTIFS($D$2:$D$111,D75,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C75="","",(COUNTIFS($D$2:$D$112,D75,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C75)+(COUNTIFS($D$2:$D$112,D75,$C$2:$C$112,C75)+1)/2)/COUNTIFS($D$2:$D$112,D75,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H75">
@@ -5944,7 +5966,7 @@
         <v/>
       </c>
       <c r="G76" s="30">
-        <f>IF(C76="","",(COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C76)+(COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,C76)+1)/2)/COUNTIFS($D$2:$D$111,D76,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C76="","",(COUNTIFS($D$2:$D$112,D76,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C76)+(COUNTIFS($D$2:$D$112,D76,$C$2:$C$112,C76)+1)/2)/COUNTIFS($D$2:$D$112,D76,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H76">
@@ -5989,7 +6011,7 @@
         <v/>
       </c>
       <c r="G77" s="30">
-        <f>IF(C77="","",(COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C77)+(COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,C77)+1)/2)/COUNTIFS($D$2:$D$111,D77,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C77="","",(COUNTIFS($D$2:$D$112,D77,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C77)+(COUNTIFS($D$2:$D$112,D77,$C$2:$C$112,C77)+1)/2)/COUNTIFS($D$2:$D$112,D77,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H77">
@@ -6034,7 +6056,7 @@
         <v/>
       </c>
       <c r="G78" s="30">
-        <f>IF(C78="","",(COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C78)+(COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,C78)+1)/2)/COUNTIFS($D$2:$D$111,D78,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C78="","",(COUNTIFS($D$2:$D$112,D78,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C78)+(COUNTIFS($D$2:$D$112,D78,$C$2:$C$112,C78)+1)/2)/COUNTIFS($D$2:$D$112,D78,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H78">
@@ -6079,7 +6101,7 @@
         <v/>
       </c>
       <c r="G79" s="30">
-        <f>IF(C79="","",(COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C79)+(COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,C79)+1)/2)/COUNTIFS($D$2:$D$111,D79,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C79="","",(COUNTIFS($D$2:$D$112,D79,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C79)+(COUNTIFS($D$2:$D$112,D79,$C$2:$C$112,C79)+1)/2)/COUNTIFS($D$2:$D$112,D79,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H79">
@@ -6124,7 +6146,7 @@
         <v/>
       </c>
       <c r="G80" s="30">
-        <f>IF(C80="","",(COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C80)+(COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,C80)+1)/2)/COUNTIFS($D$2:$D$111,D80,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C80="","",(COUNTIFS($D$2:$D$112,D80,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C80)+(COUNTIFS($D$2:$D$112,D80,$C$2:$C$112,C80)+1)/2)/COUNTIFS($D$2:$D$112,D80,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H80">
@@ -6169,7 +6191,7 @@
         <v/>
       </c>
       <c r="G81" s="30">
-        <f>IF(C81="","",(COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C81)+(COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,C81)+1)/2)/COUNTIFS($D$2:$D$111,D81,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C81="","",(COUNTIFS($D$2:$D$112,D81,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C81)+(COUNTIFS($D$2:$D$112,D81,$C$2:$C$112,C81)+1)/2)/COUNTIFS($D$2:$D$112,D81,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H81">
@@ -6214,7 +6236,7 @@
         <v/>
       </c>
       <c r="G82" s="30">
-        <f>IF(C82="","",(COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C82)+(COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,C82)+1)/2)/COUNTIFS($D$2:$D$111,D82,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C82="","",(COUNTIFS($D$2:$D$112,D82,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C82)+(COUNTIFS($D$2:$D$112,D82,$C$2:$C$112,C82)+1)/2)/COUNTIFS($D$2:$D$112,D82,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H82">
@@ -6259,7 +6281,7 @@
         <v/>
       </c>
       <c r="G83" s="30">
-        <f>IF(C83="","",(COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C83)+(COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,C83)+1)/2)/COUNTIFS($D$2:$D$111,D83,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C83="","",(COUNTIFS($D$2:$D$112,D83,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C83)+(COUNTIFS($D$2:$D$112,D83,$C$2:$C$112,C83)+1)/2)/COUNTIFS($D$2:$D$112,D83,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H83">
@@ -6304,7 +6326,7 @@
         <v/>
       </c>
       <c r="G84" s="30">
-        <f>IF(C84="","",(COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C84)+(COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,C84)+1)/2)/COUNTIFS($D$2:$D$111,D84,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C84="","",(COUNTIFS($D$2:$D$112,D84,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C84)+(COUNTIFS($D$2:$D$112,D84,$C$2:$C$112,C84)+1)/2)/COUNTIFS($D$2:$D$112,D84,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H84">
@@ -6349,7 +6371,7 @@
         <v/>
       </c>
       <c r="G85" s="30">
-        <f>IF(C85="","",(COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C85)+(COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,C85)+1)/2)/COUNTIFS($D$2:$D$111,D85,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C85="","",(COUNTIFS($D$2:$D$112,D85,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C85)+(COUNTIFS($D$2:$D$112,D85,$C$2:$C$112,C85)+1)/2)/COUNTIFS($D$2:$D$112,D85,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H85">
@@ -6394,7 +6416,7 @@
         <v/>
       </c>
       <c r="G86" s="30">
-        <f>IF(C86="","",(COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C86)+(COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,C86)+1)/2)/COUNTIFS($D$2:$D$111,D86,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C86="","",(COUNTIFS($D$2:$D$112,D86,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C86)+(COUNTIFS($D$2:$D$112,D86,$C$2:$C$112,C86)+1)/2)/COUNTIFS($D$2:$D$112,D86,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H86">
@@ -6439,7 +6461,7 @@
         <v/>
       </c>
       <c r="G87" s="30">
-        <f>IF(C87="","",(COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C87)+(COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,C87)+1)/2)/COUNTIFS($D$2:$D$111,D87,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C87="","",(COUNTIFS($D$2:$D$112,D87,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C87)+(COUNTIFS($D$2:$D$112,D87,$C$2:$C$112,C87)+1)/2)/COUNTIFS($D$2:$D$112,D87,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H87">
@@ -6484,7 +6506,7 @@
         <v/>
       </c>
       <c r="G88" s="30">
-        <f>IF(C88="","",(COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C88)+(COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,C88)+1)/2)/COUNTIFS($D$2:$D$111,D88,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C88="","",(COUNTIFS($D$2:$D$112,D88,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C88)+(COUNTIFS($D$2:$D$112,D88,$C$2:$C$112,C88)+1)/2)/COUNTIFS($D$2:$D$112,D88,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H88">
@@ -6529,7 +6551,7 @@
         <v/>
       </c>
       <c r="G89" s="30">
-        <f>IF(C89="","",(COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C89)+(COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,C89)+1)/2)/COUNTIFS($D$2:$D$111,D89,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C89="","",(COUNTIFS($D$2:$D$112,D89,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C89)+(COUNTIFS($D$2:$D$112,D89,$C$2:$C$112,C89)+1)/2)/COUNTIFS($D$2:$D$112,D89,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H89">
@@ -6574,7 +6596,7 @@
         <v/>
       </c>
       <c r="G90" s="30">
-        <f>IF(C90="","",(COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C90)+(COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,C90)+1)/2)/COUNTIFS($D$2:$D$111,D90,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C90="","",(COUNTIFS($D$2:$D$112,D90,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C90)+(COUNTIFS($D$2:$D$112,D90,$C$2:$C$112,C90)+1)/2)/COUNTIFS($D$2:$D$112,D90,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H90">
@@ -6619,7 +6641,7 @@
         <v/>
       </c>
       <c r="G91" s="30">
-        <f>IF(C91="","",(COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C91)+(COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,C91)+1)/2)/COUNTIFS($D$2:$D$111,D91,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C91="","",(COUNTIFS($D$2:$D$112,D91,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C91)+(COUNTIFS($D$2:$D$112,D91,$C$2:$C$112,C91)+1)/2)/COUNTIFS($D$2:$D$112,D91,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H91">
@@ -6664,7 +6686,7 @@
         <v/>
       </c>
       <c r="G92" s="30">
-        <f>IF(C92="","",(COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C92)+(COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,C92)+1)/2)/COUNTIFS($D$2:$D$111,D92,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C92="","",(COUNTIFS($D$2:$D$112,D92,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C92)+(COUNTIFS($D$2:$D$112,D92,$C$2:$C$112,C92)+1)/2)/COUNTIFS($D$2:$D$112,D92,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H92">
@@ -6679,7 +6701,10 @@
         <f>IFERROR((B104/B92)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K92" s="30" t="n"/>
+      <c r="K92" s="30">
+        <f>IFERROR((B112/B92)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L92" s="30" t="n"/>
     </row>
     <row r="93">
@@ -6706,7 +6731,7 @@
         <v/>
       </c>
       <c r="G93" s="30">
-        <f>IF(C93="","",(COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C93)+(COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,C93)+1)/2)/COUNTIFS($D$2:$D$111,D93,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C93="","",(COUNTIFS($D$2:$D$112,D93,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C93)+(COUNTIFS($D$2:$D$112,D93,$C$2:$C$112,C93)+1)/2)/COUNTIFS($D$2:$D$112,D93,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H93">
@@ -6748,7 +6773,7 @@
         <v/>
       </c>
       <c r="G94" s="30">
-        <f>IF(C94="","",(COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C94)+(COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,C94)+1)/2)/COUNTIFS($D$2:$D$111,D94,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C94="","",(COUNTIFS($D$2:$D$112,D94,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C94)+(COUNTIFS($D$2:$D$112,D94,$C$2:$C$112,C94)+1)/2)/COUNTIFS($D$2:$D$112,D94,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H94">
@@ -6790,7 +6815,7 @@
         <v/>
       </c>
       <c r="G95" s="30">
-        <f>IF(C95="","",(COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C95)+(COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,C95)+1)/2)/COUNTIFS($D$2:$D$111,D95,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C95="","",(COUNTIFS($D$2:$D$112,D95,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C95)+(COUNTIFS($D$2:$D$112,D95,$C$2:$C$112,C95)+1)/2)/COUNTIFS($D$2:$D$112,D95,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H95">
@@ -6832,7 +6857,7 @@
         <v/>
       </c>
       <c r="G96" s="30">
-        <f>IF(C96="","",(COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C96)+(COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,C96)+1)/2)/COUNTIFS($D$2:$D$111,D96,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C96="","",(COUNTIFS($D$2:$D$112,D96,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C96)+(COUNTIFS($D$2:$D$112,D96,$C$2:$C$112,C96)+1)/2)/COUNTIFS($D$2:$D$112,D96,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H96">
@@ -6874,7 +6899,7 @@
         <v/>
       </c>
       <c r="G97" s="30">
-        <f>IF(C97="","",(COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C97)+(COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,C97)+1)/2)/COUNTIFS($D$2:$D$111,D97,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C97="","",(COUNTIFS($D$2:$D$112,D97,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C97)+(COUNTIFS($D$2:$D$112,D97,$C$2:$C$112,C97)+1)/2)/COUNTIFS($D$2:$D$112,D97,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H97">
@@ -6916,7 +6941,7 @@
         <v/>
       </c>
       <c r="G98" s="30">
-        <f>IF(C98="","",(COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C98)+(COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,C98)+1)/2)/COUNTIFS($D$2:$D$111,D98,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C98="","",(COUNTIFS($D$2:$D$112,D98,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C98)+(COUNTIFS($D$2:$D$112,D98,$C$2:$C$112,C98)+1)/2)/COUNTIFS($D$2:$D$112,D98,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H98">
@@ -6958,7 +6983,7 @@
         <v/>
       </c>
       <c r="G99" s="30">
-        <f>IF(C99="","",(COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C99)+(COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,C99)+1)/2)/COUNTIFS($D$2:$D$111,D99,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C99="","",(COUNTIFS($D$2:$D$112,D99,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C99)+(COUNTIFS($D$2:$D$112,D99,$C$2:$C$112,C99)+1)/2)/COUNTIFS($D$2:$D$112,D99,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H99">
@@ -7000,7 +7025,7 @@
         <v/>
       </c>
       <c r="G100" s="30">
-        <f>IF(C100="","",(COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C100)+(COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,C100)+1)/2)/COUNTIFS($D$2:$D$111,D100,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C100="","",(COUNTIFS($D$2:$D$112,D100,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C100)+(COUNTIFS($D$2:$D$112,D100,$C$2:$C$112,C100)+1)/2)/COUNTIFS($D$2:$D$112,D100,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H100">
@@ -7011,7 +7036,10 @@
         <f>IFERROR(B104/B100-1,"")</f>
         <v/>
       </c>
-      <c r="J100" s="30" t="n"/>
+      <c r="J100" s="30">
+        <f>IFERROR((B112/B100)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K100" s="30" t="n"/>
       <c r="L100" s="30" t="n"/>
     </row>
@@ -7039,7 +7067,7 @@
         <v/>
       </c>
       <c r="G101" s="30">
-        <f>IF(C101="","",(COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C101)+(COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,C101)+1)/2)/COUNTIFS($D$2:$D$111,D101,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C101="","",(COUNTIFS($D$2:$D$112,D101,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C101)+(COUNTIFS($D$2:$D$112,D101,$C$2:$C$112,C101)+1)/2)/COUNTIFS($D$2:$D$112,D101,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H101">
@@ -7078,7 +7106,7 @@
         <v/>
       </c>
       <c r="G102" s="30">
-        <f>IF(C102="","",(COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C102)+(COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,C102)+1)/2)/COUNTIFS($D$2:$D$111,D102,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C102="","",(COUNTIFS($D$2:$D$112,D102,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C102)+(COUNTIFS($D$2:$D$112,D102,$C$2:$C$112,C102)+1)/2)/COUNTIFS($D$2:$D$112,D102,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H102">
@@ -7117,7 +7145,7 @@
         <v/>
       </c>
       <c r="G103" s="30">
-        <f>IF(C103="","",(COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C103)+(COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,C103)+1)/2)/COUNTIFS($D$2:$D$111,D103,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C103="","",(COUNTIFS($D$2:$D$112,D103,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C103)+(COUNTIFS($D$2:$D$112,D103,$C$2:$C$112,C103)+1)/2)/COUNTIFS($D$2:$D$112,D103,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H103">
@@ -7156,7 +7184,7 @@
         <v/>
       </c>
       <c r="G104" s="30">
-        <f>IF(C104="","",(COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C104)+(COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,C104)+1)/2)/COUNTIFS($D$2:$D$111,D104,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C104="","",(COUNTIFS($D$2:$D$112,D104,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C104)+(COUNTIFS($D$2:$D$112,D104,$C$2:$C$112,C104)+1)/2)/COUNTIFS($D$2:$D$112,D104,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H104">
@@ -7195,7 +7223,7 @@
         <v/>
       </c>
       <c r="G105" s="30">
-        <f>IF(C105="","",(COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C105)+(COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,C105)+1)/2)/COUNTIFS($D$2:$D$111,D105,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C105="","",(COUNTIFS($D$2:$D$112,D105,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C105)+(COUNTIFS($D$2:$D$112,D105,$C$2:$C$112,C105)+1)/2)/COUNTIFS($D$2:$D$112,D105,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H105">
@@ -7234,7 +7262,7 @@
         <v/>
       </c>
       <c r="G106" s="30">
-        <f>IF(C106="","",(COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C106)+(COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,C106)+1)/2)/COUNTIFS($D$2:$D$111,D106,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C106="","",(COUNTIFS($D$2:$D$112,D106,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C106)+(COUNTIFS($D$2:$D$112,D106,$C$2:$C$112,C106)+1)/2)/COUNTIFS($D$2:$D$112,D106,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H106">
@@ -7273,7 +7301,7 @@
         <v/>
       </c>
       <c r="G107" s="30">
-        <f>IF(C107="","",(COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C107)+(COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,C107)+1)/2)/COUNTIFS($D$2:$D$111,D107,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C107="","",(COUNTIFS($D$2:$D$112,D107,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C107)+(COUNTIFS($D$2:$D$112,D107,$C$2:$C$112,C107)+1)/2)/COUNTIFS($D$2:$D$112,D107,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H107">
@@ -7312,14 +7340,17 @@
         <v/>
       </c>
       <c r="G108" s="30">
-        <f>IF(C108="","",(COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C108)+(COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,C108)+1)/2)/COUNTIFS($D$2:$D$111,D108,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C108="","",(COUNTIFS($D$2:$D$112,D108,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C108)+(COUNTIFS($D$2:$D$112,D108,$C$2:$C$112,C108)+1)/2)/COUNTIFS($D$2:$D$112,D108,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H108">
         <f>IF(G108="","",IF(G108&lt;=20%,"Q1 Cheapest",IF(G108&lt;=40%,"Q2",IF(G108&lt;=60%,"Q3",IF(G108&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I108" s="30" t="n"/>
+      <c r="I108" s="30">
+        <f>IFERROR(B112/B108-1,"")</f>
+        <v/>
+      </c>
       <c r="J108" s="30" t="n"/>
       <c r="K108" s="30" t="n"/>
       <c r="L108" s="30" t="n"/>
@@ -7348,7 +7379,7 @@
         <v/>
       </c>
       <c r="G109" s="30">
-        <f>IF(C109="","",(COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C109)+(COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,C109)+1)/2)/COUNTIFS($D$2:$D$111,D109,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C109="","",(COUNTIFS($D$2:$D$112,D109,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C109)+(COUNTIFS($D$2:$D$112,D109,$C$2:$C$112,C109)+1)/2)/COUNTIFS($D$2:$D$112,D109,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H109">
@@ -7384,7 +7415,7 @@
         <v/>
       </c>
       <c r="G110" s="30">
-        <f>IF(C110="","",(COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C110)+(COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,C110)+1)/2)/COUNTIFS($D$2:$D$111,D110,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C110="","",(COUNTIFS($D$2:$D$112,D110,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C110)+(COUNTIFS($D$2:$D$112,D110,$C$2:$C$112,C110)+1)/2)/COUNTIFS($D$2:$D$112,D110,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H110">
@@ -7420,7 +7451,7 @@
         <v/>
       </c>
       <c r="G111" s="30">
-        <f>IF(C111="","",(COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,"&gt;0",$C$2:$C$111,"&lt;"&amp;C111)+(COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,C111)+1)/2)/COUNTIFS($D$2:$D$111,D111,$C$2:$C$111,"&gt;0"))</f>
+        <f>IF(C111="","",(COUNTIFS($D$2:$D$112,D111,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C111)+(COUNTIFS($D$2:$D$112,D111,$C$2:$C$112,C111)+1)/2)/COUNTIFS($D$2:$D$112,D111,$C$2:$C$112,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H111">
@@ -7431,6 +7462,42 @@
       <c r="J111" s="30" t="n"/>
       <c r="K111" s="30" t="n"/>
       <c r="L111" s="30" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B112" s="24" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="C112" s="25" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E112" s="33">
+        <f>IFERROR(B112/C112,"")</f>
+        <v/>
+      </c>
+      <c r="F112" s="30">
+        <f>IF(AND(D112=D108,E108&lt;&gt;""),E112/E108-1,"")</f>
+        <v/>
+      </c>
+      <c r="G112" s="30">
+        <f>IF(C112="","",(COUNTIFS($D$2:$D$112,D112,$C$2:$C$112,"&gt;0",$C$2:$C$112,"&lt;"&amp;C112)+(COUNTIFS($D$2:$D$112,D112,$C$2:$C$112,C112)+1)/2)/COUNTIFS($D$2:$D$112,D112,$C$2:$C$112,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H112">
+        <f>IF(G112="","",IF(G112&lt;=20%,"Q1 Cheapest",IF(G112&lt;=40%,"Q2",IF(G112&lt;=60%,"Q3",IF(G112&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I112" s="30" t="n"/>
+      <c r="J112" s="30" t="n"/>
+      <c r="K112" s="30" t="n"/>
+      <c r="L112" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -7445,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7453,7 +7520,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -7767,6 +7834,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>22620.45</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0149253731343</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.0330557356855</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -7807,7 +7907,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7816,7 +7916,7 @@
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -7836,7 +7936,7 @@
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="4"/>
@@ -7887,7 +7987,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.1038</v>
       </c>
     </row>
     <row r="7">
@@ -7910,7 +8010,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.09449999999999999</v>
+        <v>0.09050000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -7933,7 +8033,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -7956,7 +8056,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="10">
@@ -7979,7 +8079,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="11">
@@ -8002,7 +8102,7 @@
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0398</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="12">
@@ -8011,21 +8111,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0361</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="13">
@@ -8034,21 +8134,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="14">
@@ -8071,7 +8171,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.028</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="15">
@@ -8094,7 +8194,7 @@
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0266</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="16">
@@ -8117,7 +8217,7 @@
         </is>
       </c>
       <c r="E16" s="37" t="n">
-        <v>0.0257</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="17">
@@ -8140,7 +8240,7 @@
         </is>
       </c>
       <c r="E17" s="37" t="n">
-        <v>0.0224</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="18">
@@ -8149,17 +8249,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E18" s="37" t="n">
@@ -8172,21 +8272,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E19" s="37" t="n">
-        <v>0.0215</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20">
@@ -8209,7 +8309,7 @@
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>0.0191</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="21">
@@ -8232,7 +8332,7 @@
         </is>
       </c>
       <c r="E21" s="37" t="n">
-        <v>0.0191</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="22">
@@ -8241,21 +8341,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>0.016</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="23">
@@ -8264,21 +8364,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E23" s="37" t="n">
-        <v>0.0158</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="24">
@@ -8301,7 +8401,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.0141</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="25">
@@ -8310,21 +8410,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E25" s="37" t="n">
-        <v>0.0141</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="26">
@@ -8333,21 +8433,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E26" s="37" t="n">
-        <v>0.0138</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="27">
@@ -8370,7 +8470,7 @@
         </is>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.0135</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="28">
@@ -8379,21 +8479,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.0133</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="29">
@@ -8402,21 +8502,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.0126</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="30">
@@ -8425,21 +8525,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.0123</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="31">
@@ -8448,21 +8548,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E31" s="37" t="n">
-        <v>0.0122</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="32">
@@ -8471,21 +8571,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E32" s="37" t="n">
-        <v>0.0115</v>
+        <v>0.0121</v>
       </c>
     </row>
     <row r="33">
@@ -8508,7 +8608,7 @@
         </is>
       </c>
       <c r="E33" s="37" t="n">
-        <v>0.0111</v>
+        <v>0.0115</v>
       </c>
     </row>
     <row r="34">
@@ -8517,21 +8617,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E34" s="37" t="n">
-        <v>0.0109</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="35">
@@ -8540,21 +8640,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E35" s="37" t="n">
-        <v>0.0108</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="36">
@@ -8563,21 +8663,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>0.0108</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="37">
@@ -8586,12 +8686,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8600,7 +8700,7 @@
         </is>
       </c>
       <c r="E37" s="37" t="n">
-        <v>0.0107</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="38">
@@ -8609,21 +8709,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="E38" s="37" t="n">
-        <v>0.0106</v>
+        <v>0.0104</v>
       </c>
     </row>
     <row r="39">
@@ -8632,21 +8732,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E39" s="37" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="40">
@@ -8655,21 +8755,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -8678,17 +8778,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E41" s="37" t="n">
@@ -8701,21 +8801,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.009399999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -8724,21 +8824,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E43" s="37" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="44">
@@ -8747,21 +8847,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E44" s="37" t="n">
-        <v>0.0083</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -8784,7 +8884,7 @@
         </is>
       </c>
       <c r="E45" s="37" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -8793,21 +8893,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>0.0075</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="47">
@@ -8816,12 +8916,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8830,7 +8930,7 @@
         </is>
       </c>
       <c r="E47" s="37" t="n">
-        <v>0.0072</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="48">
@@ -8839,12 +8939,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8853,7 +8953,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="49">
@@ -8862,21 +8962,21 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E49" s="37" t="n">
-        <v>0.0071</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="50">
@@ -8885,12 +8985,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8899,7 +8999,7 @@
         </is>
       </c>
       <c r="E50" s="37" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="51">
@@ -8908,21 +9008,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Jio Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E51" s="37" t="n">
-        <v>0.0064</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="52">
@@ -8931,21 +9031,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>0.0061</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="53">
@@ -8954,17 +9054,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E53" s="37" t="n">
@@ -8977,21 +9077,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E54" s="37" t="n">
-        <v>0.0053</v>
+        <v>0.005699999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -9000,21 +9100,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E55" s="37" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.0054</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22620.45</v>
+        <v>22421.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.36</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.411673553719</v>
+        <v>1168.418447107869</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03305573568548059</v>
+        <v>0.03310352582666498</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05165289256198347</v>
+        <v>0.05211047420531526</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>98.50746268656717</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.22229427419224</v>
+        <v>33.24141033066599</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.92191216285468</v>
+        <v>79.4500350394983</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44397163237557</v>
+        <v>20.44402570350674</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23886.9751090687</v>
+        <v>23887.1767651247</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05599027026733316</v>
+        <v>0.06534787407539033</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25950.4232696281</v>
+        <v>25950.57371026576</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.147210743801653</v>
+        <v>0.1573736321000521</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7867,6 +7867,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>22421.95</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0331035258267</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22421.95</v>
+        <v>22555.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.19</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.418447107869</v>
+        <v>1168.691709844559</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03310352582666498</v>
+        <v>0.03328698529494778</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05211047420531526</v>
+        <v>0.05181347150259067</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.24141033066599</v>
+        <v>33.31479411797911</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.4500350394983</v>
+        <v>79.47205017569223</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44402570350674</v>
+        <v>20.44423327479085</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23887.1767651247</v>
+        <v>23893.00594237636</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06534787407539033</v>
+        <v>0.05928669817569188</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25950.57371026576</v>
+        <v>25956.64287564767</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1573736321000521</v>
+        <v>0.1507772020725389</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7900,6 +7900,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>22555.75</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.0332869852949</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,8 +569,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22555.75</v>
+        <v>22776.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.3</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.691709844559</v>
+        <v>1168.604412519241</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03328698529494778</v>
+        <v>0.03357554913146776</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05181347150259067</v>
+        <v>0.05130836326321191</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.31479411797911</v>
+        <v>33.43021965258711</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.47205017569223</v>
+        <v>78.46190171667165</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44423327479085</v>
+        <v>20.44455976416018</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23893.00594237636</v>
+        <v>23891.60275241091</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05928669817569188</v>
+        <v>0.04897689913597625</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25956.64287564767</v>
+        <v>25954.70400205233</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1507772020725389</v>
+        <v>0.1395587480759364</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7933,6 +7933,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>22776.1</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.0335755491315</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22776.1</v>
+        <v>22603.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.49</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.604412519241</v>
+        <v>1168.720268872803</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03357554913146776</v>
+        <v>0.03334713895310393</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05130836326321191</v>
+        <v>0.05170630816959669</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.43021965258711</v>
+        <v>33.33885558124157</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.46190171667165</v>
+        <v>79.47926861467097</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44455976416018</v>
+        <v>20.44430133435837</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23891.60275241091</v>
+        <v>23893.66935240791</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04897689913597625</v>
+        <v>0.05709934510643078</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25954.70400205233</v>
+        <v>25957.27717166494</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1395587480759364</v>
+        <v>0.1483971044467425</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7966,6 +7966,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>22603.05</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.0333471389531</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22603.05</v>
+        <v>22231.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.34</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.720268872803</v>
+        <v>1168.864353312303</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03334713895310393</v>
+        <v>0.03370559650355465</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05170630816959669</v>
+        <v>0.05257623554153523</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.33885558124157</v>
+        <v>33.48223860142186</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.47926861467097</v>
+        <v>79.52228352072505</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44430133435837</v>
+        <v>20.44470690347259</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23893.66935240791</v>
+        <v>23897.08911338707</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05709934510643078</v>
+        <v>0.07490572573462639</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25957.27717166494</v>
+        <v>25960.47728706625</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1483971044467425</v>
+        <v>0.1677181913774974</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7999,6 +7999,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>22231.8</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.0337055965036</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22231.8</v>
+        <v>22520.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.02</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.864353312303</v>
+        <v>1168.679294239751</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03370559650355465</v>
+        <v>0.03354358634884136</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05257623554153523</v>
+        <v>0.05189413596263622</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.48223860142186</v>
+        <v>33.41743453953654</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.52228352072505</v>
+        <v>79.50284230215946</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44470690347259</v>
+        <v>20.44452360055469</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23897.08911338707</v>
+        <v>23893.09141256419</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07490572573462639</v>
+        <v>0.06095088741851007</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25960.47728706625</v>
+        <v>25956.36712506487</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1677181913774974</v>
+        <v>0.1525687597301506</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8032,6 +8032,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>22520.45</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.0335435863488</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22520.45</v>
+        <v>22363.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.27</v>
+        <v>19.12</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1168.679294239751</v>
+        <v>1169.631276150627</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03354358634884136</v>
+        <v>0.03431256971835595</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05189413596263622</v>
+        <v>0.05230125523012552</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.41743453953654</v>
+        <v>33.72502788734238</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.50284230215946</v>
+        <v>79.59512030650122</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44452360055469</v>
+        <v>20.44539365030991</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23893.09141256419</v>
+        <v>23913.57186661391</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06095088741851007</v>
+        <v>0.06931975158524617</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25956.36712506487</v>
+        <v>25977.51064330544</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1525687597301506</v>
+        <v>0.1616108786610877</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8065,6 +8065,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>22363.35</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0343125697184</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22363.35</v>
+        <v>22721.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.12</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1169.631276150627</v>
+        <v>1170.631117980422</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03431256971835595</v>
+        <v>0.03525658629000761</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05230125523012552</v>
+        <v>0.05151983513652756</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.72502788734238</v>
+        <v>34.10263451600304</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.59512030650122</v>
+        <v>78.66362617569644</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44539365030991</v>
+        <v>20.44646173763098</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23913.57186661391</v>
+        <v>23935.26436266688</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06931975158524617</v>
+        <v>0.05339833784806691</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25977.51064330544</v>
+        <v>25999.71713034518</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1616108786610877</v>
+        <v>0.1442555383822772</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8098,6 +8098,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>22721.95</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.03525658629</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,8 +569,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22721.95</v>
+        <v>22622.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.41</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1170.631117980422</v>
+        <v>1170.341438178996</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03525658629000761</v>
+        <v>0.03464596729908287</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05151983513652756</v>
+        <v>0.05173305742369375</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>34.10263451600304</v>
+        <v>33.85838691963315</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.66362617569644</v>
+        <v>79.63512801618845</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44646173763098</v>
+        <v>20.44577086585839</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23935.26436266688</v>
+        <v>23928.53287982694</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05339833784806691</v>
+        <v>0.05772223827513678</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25999.71713034518</v>
+        <v>25993.28334195551</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1442555383822772</v>
+        <v>0.148991205380238</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8131,6 +8131,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>22622.7</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0346459672991</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22622.7</v>
+        <v>22997.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.33</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1170.341438178996</v>
+        <v>1170.348600508906</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03464596729908287</v>
+        <v>0.0347721849975382</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05173305742369375</v>
+        <v>0.05089058524173028</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>99.25373134328358</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.85838691963315</v>
+        <v>33.90887399901528</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>79.63512801618845</v>
+        <v>76.51594578179414</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44577086585839</v>
+        <v>20.44591367216864</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23928.53287982694</v>
+        <v>23928.84645234848</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05772223827513678</v>
+        <v>0.04050451257855725</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>22.21</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25993.28334195551</v>
+        <v>25993.4424173028</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.148991205380238</v>
+        <v>0.1302798982188298</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8164,6 +8164,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>22997.35</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.0347721849975</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,8 +569,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22997.35</v>
+        <v>23146.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.65</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1170.348600508906</v>
+        <v>1170.771370763784</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0347721849975382</v>
+        <v>0.03874139120267839</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05089058524173028</v>
+        <v>0.05058168942842691</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>33.90887399901528</v>
+        <v>35.49655648107135</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.51594578179414</v>
+        <v>75.94747440700796</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.44591367216864</v>
+        <v>20.45525909117539</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23928.84645234848</v>
+        <v>23948.43172550376</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04050451257855725</v>
+        <v>0.0346615625278397</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.21</v>
+        <v>22.24587857165391</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25993.4424173028</v>
+        <v>26044.83774917993</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1302798982188298</v>
+        <v>0.1252341209738952</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8197,6 +8197,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>23146.15</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0387413912027</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -569,8 +569,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>23146.15</v>
+        <v>22888.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.77</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1170.771370763784</v>
+        <v>1184.115364718055</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.03874139120267839</v>
+        <v>0.04917562756209382</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05058168942842691</v>
+        <v>0.05173305742369375</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>99.25373134328358</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>35.49655648107135</v>
+        <v>39.67025102483753</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.94747440700796</v>
+        <v>81.37868724774975</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.45525909117539</v>
+        <v>20.59326083167867</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23948.43172550376</v>
+        <v>24384.79656043722</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0346615625278397</v>
+        <v>0.06535234514633581</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.24587857165391</v>
+        <v>22.34026912588102</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26044.83774917993</v>
+        <v>26453.45592389211</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1252341209738952</v>
+        <v>0.1557304255499752</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8230,6 +8230,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>22888.95</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.0491756275621</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22888.95</v>
+        <v>22811.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.33</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1184.115364718055</v>
+        <v>1184.389927310488</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04917562756209382</v>
+        <v>0.04114745084931126</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05173305742369375</v>
+        <v>0.05192107995846313</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.67025102483753</v>
+        <v>36.4589803397245</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.37868724774975</v>
+        <v>80.41530604221586</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.59326083167867</v>
+        <v>20.4906487913493</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24384.79656043722</v>
+        <v>24268.91803253093</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06535234514633581</v>
+        <v>0.06389661429643279</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.34026912588102</v>
+        <v>22.27582370257029</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26453.45592389211</v>
+        <v>26383.26121586846</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1557304255499752</v>
+        <v>0.1565848236017799</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8263,6 +8263,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>22811.35</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.0411474508493</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22811.35</v>
+        <v>22687.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.26</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1184.389927310488</v>
+        <v>1185.972294824883</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04114745084931126</v>
+        <v>0.04253844368531068</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05192107995846313</v>
+        <v>0.05227391531625719</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>36.4589803397245</v>
+        <v>37.01537747412427</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.41530604221586</v>
+        <v>80.58222518253578</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.4906487913493</v>
+        <v>20.51110830883422</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24268.91803253093</v>
+        <v>24325.60619042984</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06389661429643279</v>
+        <v>0.07219593877857955</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.27582370257029</v>
+        <v>22.29313560198061</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26383.26121586846</v>
+        <v>26439.04118872323</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1565848236017799</v>
+        <v>0.1653494825917727</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8296,6 +8296,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>22687.65</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.0425384436853</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22687.65</v>
+        <v>22600</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.13</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1185.972294824883</v>
+        <v>1186.351706036745</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04253844368531068</v>
+        <v>0.04287001975159033</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05227391531625719</v>
+        <v>0.05249343832020997</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>37.01537747412427</v>
+        <v>37.14800790063613</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.58222518253578</v>
+        <v>80.62201431048933</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.51110830883422</v>
+        <v>20.5159853190891</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24325.60619042984</v>
+        <v>24339.17418432618</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07219593877857955</v>
+        <v>0.07695460992593728</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29313560198061</v>
+        <v>22.29726230296551</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26439.04118872323</v>
+        <v>26452.39517307194</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1653494825917727</v>
+        <v>0.1704599634102628</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8329,6 +8329,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>22600</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.0428700197516</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22600</v>
+        <v>22753.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.05</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1186.351706036745</v>
+        <v>1186.298227320125</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04287001975159033</v>
+        <v>0.0425750892453518</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05249343832020997</v>
+        <v>0.05213764337851929</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>37.14800790063613</v>
+        <v>37.03003569814072</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.62201431048933</v>
+        <v>80.58662264974072</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.5159853190891</v>
+        <v>20.51164731267163</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24339.17418432618</v>
+        <v>24332.93084643796</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07695460992593728</v>
+        <v>0.06942895269403704</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29726230296551</v>
+        <v>22.29359168215072</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26452.39517307194</v>
+        <v>26446.84829313408</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1704599634102628</v>
+        <v>0.1623353327502981</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8362,6 +8362,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>22753.2</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.0425750892454</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22753.2</v>
+        <v>22749.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.18</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1186.298227320125</v>
+        <v>1192.960146827478</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.0425750892453518</v>
+        <v>0.04933980153082929</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05213764337851929</v>
+        <v>0.05243838489774515</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>37.03003569814072</v>
+        <v>39.73592061233171</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.58662264974072</v>
+        <v>81.39838812399802</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.51164731267163</v>
+        <v>20.59437533839214</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24332.93084643796</v>
+        <v>24568.26902750848</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06942895269403704</v>
+        <v>0.0799357807232377</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.29359168215072</v>
+        <v>22.34101213035667</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26446.84829313408</v>
+        <v>26651.93711130475</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1623353327502981</v>
+        <v>0.1715265930968362</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8395,6 +8395,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>22749.75</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0493398015308</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22749.75</v>
+        <v>22698.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.07</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1192.960146827478</v>
+        <v>1195.30542390732</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.04933980153082929</v>
+        <v>0.05169106397872603</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05243838489774515</v>
+        <v>0.05265929436545551</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>39.73592061233171</v>
+        <v>40.67642559149041</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.39838812399802</v>
+        <v>81.68053961774562</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.59437533839214</v>
+        <v>20.61033705146701</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24568.26902750848</v>
+        <v>24635.64766617651</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0799357807232377</v>
+        <v>0.08532580576445548</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.34101213035667</v>
+        <v>22.35165327240658</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26651.93711130475</v>
+        <v>26717.05238980338</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1715265930968362</v>
+        <v>0.177022289226255</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8428,6 +8428,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>22698.85</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.0516910639787</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22698.85</v>
+        <v>22936.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.99</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1195.30542390732</v>
+        <v>1195.244919228765</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.05169106397872603</v>
+        <v>0.05147457957247448</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05265929436545551</v>
+        <v>0.05211047420531526</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>40.67642559149041</v>
+        <v>40.58983182898979</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.68053961774562</v>
+        <v>81.65456148899544</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.61033705146701</v>
+        <v>20.608867431612</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24635.64766617651</v>
+        <v>24632.64408869341</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08532580576445548</v>
+        <v>0.07393785469577896</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.35165327240658</v>
+        <v>22.35067352583657</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26717.05238980338</v>
+        <v>26714.52897309703</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.177022289226255</v>
+        <v>0.1647041962395295</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8461,6 +8461,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>22936.75</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.0514745795725</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-50.xlsx
+++ b/docs/downloads/indices/nifty-50.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22936.75</v>
+        <v>23053.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.19</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1195.244919228765</v>
+        <v>1194.461139896373</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.05147457957247448</v>
+        <v>0.0510100396841473</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05211047420531526</v>
+        <v>0.05181347150259067</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>40.58983182898979</v>
+        <v>40.40401587365892</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.65456148899544</v>
+        <v>81.59881670239618</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20.608867431612</v>
+        <v>20.60571386939867</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24632.64408869341</v>
+        <v>24612.72447682043</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07393785469577896</v>
+        <v>0.06765356836262515</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>22.35067352583657</v>
+        <v>22.34857115102768</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>26714.52897309703</v>
+        <v>26694.49977211173</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1647041962395295</v>
+        <v>0.1579570544573929</v>
       </c>
     </row>
     <row r="16">
@@ -7512,7 +7512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -8494,6 +8494,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.00746268656716</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0510100396841</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -8534,7 +8567,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -8543,7 +8576,7 @@
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="3">
@@ -8563,7 +8596,7 @@
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5304</v>
       </c>
     </row>
     <row r="4"/>
@@ -8614,7 +8647,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.1038</v>
+        <v>0.09949999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -8637,7 +8670,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.09390000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -8660,7 +8693,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="9">
@@ -8683,7 +8716,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.051</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="10">
@@ -8706,7 +8739,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.042</v>
+        <v>0.0425</v>
       </c>
     </row>
     <row r="11">
@@ -8715,21 +8748,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0379</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="12">
@@ -8738,12 +8771,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8752,7 +8785,7 @@
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0337</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="13">
@@ -8761,21 +8794,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0335</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="14">
@@ -8798,7 +8831,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.0293</v>
+        <v>0.0319</v>
       </c>
     </row>
     <row r="15">
@@ -8807,21 +8840,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0252</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="16">
@@ -8830,21 +8863,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E16" s="37" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="17">
@@ -8853,21 +8886,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E17" s="37" t="n">
-        <v>0.0242</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="18">
@@ -8876,21 +8909,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E18" s="37" t="n">
-        <v>0.0222</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="19">
@@ -8899,21 +8932,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E19" s="37" t="n">
-        <v>0.02</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="20">
@@ -8936,7 +8969,7 @@
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>0.0184</v>
+        <v>0.0176</v>
       </c>
     </row>
     <row r="21">
@@ -8959,7 +8992,7 @@
         </is>
       </c>
       <c r="E21" s="37" t="n">
-        <v>0.0181</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="22">
@@ -8982,7 +9015,7 @@
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>0.0159</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="23">
@@ -8991,21 +9024,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" s="37" t="n">
-        <v>0.0149</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="24">
@@ -9028,7 +9061,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.0147</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="25">
@@ -9037,21 +9070,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E25" s="37" t="n">
-        <v>0.0146</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="26">
@@ -9074,7 +9107,7 @@
         </is>
       </c>
       <c r="E26" s="37" t="n">
-        <v>0.0135</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="27">
@@ -9083,21 +9116,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E27" s="37" t="n">
-        <v>0.0133</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="28">
@@ -9106,21 +9139,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E28" s="37" t="n">
-        <v>0.0132</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="29">
@@ -9129,21 +9162,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E29" s="37" t="n">
-        <v>0.013</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="30">
@@ -9152,21 +9185,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E30" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="31">
@@ -9175,21 +9208,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E31" s="37" t="n">
-        <v>0.0124</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="32">
@@ -9198,21 +9231,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E32" s="37" t="n">
-        <v>0.0121</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="33">
@@ -9221,21 +9254,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E33" s="37" t="n">
-        <v>0.0115</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="34">
@@ -9244,21 +9277,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E34" s="37" t="n">
-        <v>0.0113</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="35">
@@ -9267,21 +9300,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E35" s="37" t="n">
-        <v>0.0113</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="36">
@@ -9290,21 +9323,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E36" s="37" t="n">
-        <v>0.011</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="37">
@@ -9313,21 +9346,21 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="E37" s="37" t="n">
-        <v>0.0108</v>
+        <v>0.0105</v>
       </c>
     </row>
     <row r="38">
@@ -9336,17 +9369,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E38" s="37" t="n">
@@ -9359,21 +9392,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
       <c r="E39" s="37" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="40">
@@ -9382,21 +9415,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
       <c r="E40" s="37" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.009399999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -9405,21 +9438,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E41" s="37" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.009300000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -9428,21 +9461,21 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E42" s="37" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="43">
@@ -9451,21 +9484,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E43" s="37" t="n">
-        <v>0.0092</v>
+        <v>0.008699999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -9474,21 +9507,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="E44" s="37" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.008199999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -9497,21 +9530,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E45" s="37" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.008199999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -9520,21 +9553,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>0.0083</v>
+        <v>0.008199999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -9543,21 +9576,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E47" s="37" t="n">
-        <v>0.008</v>
+        <v>0.007800000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -9566,21 +9599,21 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>0.0073</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="49">
@@ -9603,7 +9636,7 @@
         </is>
       </c>
       <c r="E49" s="37" t="n">
-        <v>0.0072</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="50">
@@ -9612,21 +9645,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E50" s="37" t="n">
-        <v>0.0072</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -9649,7 +9682,7 @@
         </is>
       </c>
       <c r="E51" s="37" t="n">
-        <v>0.0068</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="52">
@@ -9658,21 +9691,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
       <c r="E52" s="37" t="n">
-        <v>0.0066</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="53">
@@ -9681,21 +9714,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E53" s="37" t="n">
-        <v>0.0059</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="54">
@@ -9704,21 +9737,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E54" s="37" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="55">
@@ -9727,21 +9760,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
       <c r="E55" s="37" t="n">
-        <v>0.0054</v>
+        <v>0.0052</v>
       </c>
     </row>
   </sheetData>
